--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G38" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G29" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI39"/>
+  <dimension ref="A1:BI41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8037,12 +8037,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,141 +8090,535 @@
         </is>
       </c>
       <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI39" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI40" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N41" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P41" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="Q41" t="n">
         <v>3.25</v>
       </c>
-      <c r="R39" t="n">
+      <c r="R41" t="n">
         <v>3.35</v>
       </c>
-      <c r="S39" t="n">
-        <v>0</v>
-      </c>
-      <c r="T39" t="n">
-        <v>0</v>
-      </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI39" s="3" t="n">
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="3" t="n">
         <v>46160.875</v>
       </c>
     </row>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.99</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G40" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI41"/>
+  <dimension ref="A1:BI46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1527,7 +1527,7 @@
         <v>0</v>
       </c>
       <c r="BI5" s="3" t="n">
-        <v>46160.51388888889</v>
+        <v>46160.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -2816,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46160.54166666666</v>
+        <v>46160.51388888889</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2968,13 +2968,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>3.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.05</v>
+        <v>3.26</v>
       </c>
       <c r="R13" t="n">
-        <v>3.13</v>
+        <v>2.04</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -3013,10 +3013,10 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46160.5625</v>
+        <v>46160.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3703,12 +3703,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46160.58333333334</v>
+        <v>46160.5625</v>
       </c>
     </row>
     <row r="18">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5673,27 +5673,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46160.58680555555</v>
+        <v>46160.58333333334</v>
       </c>
     </row>
     <row r="28">
@@ -5870,12 +5870,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6058,7 +6058,7 @@
         <v>0</v>
       </c>
       <c r="BI28" s="3" t="n">
-        <v>46160.60416666666</v>
+        <v>46160.58680555555</v>
       </c>
     </row>
     <row r="29">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6461,27 +6461,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6649,7 +6649,7 @@
         <v>0</v>
       </c>
       <c r="BI31" s="3" t="n">
-        <v>46160.64583333334</v>
+        <v>46160.60416666666</v>
       </c>
     </row>
     <row r="32">
@@ -6658,12 +6658,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>3.99</v>
+        <v>2.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6846,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="BI32" s="3" t="n">
-        <v>46160.64583333334</v>
+        <v>46160.60416666666</v>
       </c>
     </row>
     <row r="33">
@@ -6855,27 +6855,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6904,138 +6904,138 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU33" t="n">
         <v>3.4</v>
       </c>
-      <c r="R33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.57</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="AV33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>1.3</v>
       </c>
-      <c r="AN33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
+      <c r="BC33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.13</v>
       </c>
-      <c r="AQ33" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.15</v>
-      </c>
       <c r="BG33" t="n">
         <v>0</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>0</v>
       </c>
       <c r="BI33" s="3" t="n">
-        <v>46160.65625</v>
+        <v>46160.60416666666</v>
       </c>
     </row>
     <row r="34">
@@ -7052,27 +7052,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -7240,7 +7240,7 @@
         <v>0</v>
       </c>
       <c r="BI34" s="3" t="n">
-        <v>46160.66666666666</v>
+        <v>46160.60416666666</v>
       </c>
     </row>
     <row r="35">
@@ -7249,12 +7249,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Londrina</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7437,7 +7437,7 @@
         <v>0</v>
       </c>
       <c r="BI35" s="3" t="n">
-        <v>46160.79166666666</v>
+        <v>46160.60416666666</v>
       </c>
     </row>
     <row r="36">
@@ -7446,27 +7446,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7634,7 +7634,7 @@
         <v>0</v>
       </c>
       <c r="BI36" s="3" t="n">
-        <v>46160.83333333334</v>
+        <v>46160.64583333334</v>
       </c>
     </row>
     <row r="37">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7831,7 +7831,7 @@
         <v>0</v>
       </c>
       <c r="BI37" s="3" t="n">
-        <v>46160.83333333334</v>
+        <v>46160.64583333334</v>
       </c>
     </row>
     <row r="38">
@@ -7840,12 +7840,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7889,137 +7889,137 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK38" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AL38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO38" t="n">
         <v>0</v>
       </c>
       <c r="AP38" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR38" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AS38" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AT38" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AU38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AV38" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AW38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY38" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB38" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC38" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="BD38" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="BE38" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BF38" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG38" t="n">
         <v>0</v>
@@ -8028,7 +8028,7 @@
         <v>0</v>
       </c>
       <c r="BI38" s="3" t="n">
-        <v>46160.83333333334</v>
+        <v>46160.65625</v>
       </c>
     </row>
     <row r="39">
@@ -8037,27 +8037,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -8225,7 +8225,7 @@
         <v>0</v>
       </c>
       <c r="BI39" s="3" t="n">
-        <v>46160.83333333334</v>
+        <v>46160.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -8234,12 +8234,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Londrina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8422,7 +8422,7 @@
         <v>0</v>
       </c>
       <c r="BI40" s="3" t="n">
-        <v>46160.83333333334</v>
+        <v>46160.79166666666</v>
       </c>
     </row>
     <row r="41">
@@ -8431,12 +8431,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,141 +8484,1126 @@
         </is>
       </c>
       <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI41" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Chile Primera B</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Unión Española</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Deportes Iquique</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N42" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI42" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Inter de Limeira</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N43" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI43" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Bolivia LFPB</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Real Potosí</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>San Antonio Bulo Bulo</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI44" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Confiança</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Maranhão</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI45" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N46" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P46" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="Q46" t="n">
         <v>3.25</v>
       </c>
-      <c r="R41" t="n">
+      <c r="R46" t="n">
         <v>3.35</v>
       </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" t="n">
-        <v>0</v>
-      </c>
-      <c r="W41" t="n">
-        <v>0</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI41" s="3" t="n">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
         <v>46160.875</v>
       </c>
     </row>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1007,70 +1007,70 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS31" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT31" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G44" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1204,70 +1204,70 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>8.1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.19</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.36</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS34" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT34" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>4.97</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>5.7</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>3.13</v>
+        <v>4.97</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>4.97</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>2.55</v>
+        <v>5.7</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G45" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI46"/>
+  <dimension ref="A1:BI48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>4.97</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>2.39</v>
+        <v>2.99</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.19</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.36</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="S35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,141 +9469,535 @@
         </is>
       </c>
       <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI46" s="3" t="n">
+        <v>46160.83333333334</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>India Indian Super League</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Jamshedpur</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Odisha FC</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N47" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI47" s="3" t="n">
+        <v>46160.875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Guayaquil City FC</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Orense SC</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P48" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q46" t="n">
+      <c r="Q48" t="n">
         <v>3.25</v>
       </c>
-      <c r="R46" t="n">
+      <c r="R48" t="n">
         <v>3.35</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI46" s="3" t="n">
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI48" s="3" t="n">
         <v>46160.875</v>
       </c>
     </row>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>3.13</v>
+        <v>4.97</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U31" t="n">
+        <v>6</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU31" t="n">
         <v>3.4</v>
       </c>
-      <c r="R31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.4</v>
       </c>
-      <c r="R34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>2.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>2.61</v>
       </c>
       <c r="R26" t="n">
-        <v>2.12</v>
+        <v>2.97</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.36</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="S33" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U33" t="n">
-        <v>9.15</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>1.3</v>
       </c>
-      <c r="W33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="BC33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R34" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S34" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T34" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X34" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI34" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU29" t="n">
         <v>3.4</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.78</v>
+        <v>2.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
-        <v>2.97</v>
+        <v>2.39</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="R25" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>5.7</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q31" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R31" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U31" t="n">
+        <v>6</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X31" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU31" t="n">
         <v>3.4</v>
       </c>
-      <c r="R31" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
       <c r="AV31" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW31" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX31" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.19</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.36</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>12</v>
+        <v>2.65</v>
       </c>
       <c r="S33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.97</v>
+        <v>3.13</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R31" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T31" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V31" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X31" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB31" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC31" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI31" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
       </c>
       <c r="AP31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV31" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW31" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX31" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U33" t="n">
+        <v>6</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU33" t="n">
         <v>3.4</v>
       </c>
-      <c r="R33" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jamshedpur</t>
+          <t>Guayaquil City FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Orense SC</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Guayaquil City FC</t>
+          <t>Jamshedpur</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Orense SC</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
         <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>3.78</v>
+        <v>2.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.78</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.61</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>2.99</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.19</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.36</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="S31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,14 +7105,14 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R34" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.55</v>
-      </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7347,10 +7347,10 @@
         <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>4.71</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>4.97</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>4.97</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
         <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>2.39</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.58</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>1.87</v>
+        <v>2.99</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.7</v>
+        <v>3.62</v>
       </c>
       <c r="R22" t="n">
-        <v>3.78</v>
+        <v>4.24</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.61</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
-        <v>2.97</v>
+        <v>1.87</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.59</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="R25" t="n">
-        <v>2.39</v>
+        <v>2.97</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="R26" t="n">
-        <v>4.24</v>
+        <v>2.65</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.18</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.99</v>
+        <v>3.78</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.4</v>
       </c>
-      <c r="R34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI48"/>
+  <dimension ref="A1:BI47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>3.24</v>
+        <v>1.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>3.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="R19" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.15</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="R20" t="n">
-        <v>2.12</v>
+        <v>4.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>4.24</v>
+        <v>3.24</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.58</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>1.87</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="R24" t="n">
-        <v>2.59</v>
+        <v>3.78</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>2.61</v>
       </c>
       <c r="R27" t="n">
-        <v>3.78</v>
+        <v>2.97</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU30" t="n">
         <v>3.4</v>
       </c>
-      <c r="R30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.19</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.36</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>12</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.57</v>
+        <v>2.01</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.33</v>
+        <v>1.76</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R34" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S34" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T34" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V34" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X34" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA34" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB34" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB34" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC34" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI34" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN34" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS34" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV34" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW34" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX34" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ34" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9801,203 +9801,6 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46160.875</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>India Indian Super League</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>Jamshedpur</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Odisha FC</t>
-        </is>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI48" s="3" t="n">
         <v>46160.875</v>
       </c>
     </row>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,13 +998,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>4.71</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.13</v>
+        <v>4.97</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,13 +4150,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.09</v>
+        <v>1.78</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.57</v>
+        <v>3.62</v>
       </c>
       <c r="R19" t="n">
-        <v>2.59</v>
+        <v>4.24</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -4195,10 +4195,10 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>3.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>4.24</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>3.78</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>3.78</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>2.61</v>
       </c>
       <c r="R25" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="R27" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>1.19</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>6.36</v>
       </c>
       <c r="R32" t="n">
-        <v>2.65</v>
+        <v>12</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE32" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK32" t="n">
         <v>2.01</v>
       </c>
-      <c r="AF32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7889,7 +7889,7 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI42" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD42" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G46" t="n">

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,79 +998,79 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
@@ -1112,19 +1112,19 @@
         <v>0</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>4.71</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,13 +3165,13 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="R20" t="n">
-        <v>1.87</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>2.18</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="R21" t="n">
-        <v>3.78</v>
+        <v>2.99</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>2.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>2.61</v>
       </c>
       <c r="R22" t="n">
-        <v>2.99</v>
+        <v>2.97</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.7</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24</v>
+        <v>3.78</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5180,10 +5180,10 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="R25" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>2.39</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.36</v>
+        <v>5.6</v>
       </c>
       <c r="R32" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="S32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>4.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>2.55</v>
+        <v>1.66</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
-        <v>4.13</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>5.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
         <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE3" t="n">
         <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AN3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1401,124 +1401,124 @@
         <v>4.71</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2977,40 +2977,40 @@
         <v>2.04</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE13" t="n">
         <v>1.93</v>
@@ -3019,28 +3019,28 @@
         <v>1.83</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO13" t="n">
         <v>0</v>
@@ -3082,19 +3082,19 @@
         <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG13" t="n">
         <v>0</v>
@@ -3174,124 +3174,124 @@
         <v>3.13</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3362,13 +3362,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -3568,124 +3568,124 @@
         <v>4.97</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3765,124 +3765,124 @@
         <v>3.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="R18" t="n">
-        <v>1.87</v>
+        <v>2.97</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.78</v>
+        <v>3.09</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.62</v>
+        <v>2.57</v>
       </c>
       <c r="R19" t="n">
-        <v>4.24</v>
+        <v>2.59</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.98</v>
+        <v>3.28</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="R21" t="n">
-        <v>2.99</v>
+        <v>4.24</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q24" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W24" t="n">
         <v>3.35</v>
       </c>
-      <c r="R24" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.09</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.57</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>2.59</v>
+        <v>2.99</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>5.7</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>2.99</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
         <v>7</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AJ29" t="n">
         <v>1.06</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD29" t="n">
         <v>3.6</v>
       </c>
-      <c r="BB29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>4.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R30" t="n">
-        <v>2.65</v>
+        <v>1.66</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.63</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.66</v>
+        <v>5.7</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR33" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS33" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW33" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX33" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA33" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,14 +7105,14 @@
         </is>
       </c>
       <c r="P34" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R34" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R34" t="n">
-        <v>2.55</v>
-      </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.36</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD5" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.59</v>
-      </c>
       <c r="BE5" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AK14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA14" t="n">
         <v>2.85</v>
       </c>
-      <c r="AE14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="BB14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="BE15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BF15" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.33</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="S18" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.57</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>2.59</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="R20" t="n">
-        <v>1.87</v>
+        <v>4.24</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>3.58</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="R21" t="n">
-        <v>4.24</v>
+        <v>1.87</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="R22" t="n">
-        <v>2.65</v>
+        <v>2.99</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24</v>
+        <v>2.12</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q24" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U24" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X24" t="n">
         <v>3.7</v>
       </c>
-      <c r="R24" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U24" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.41</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AI24" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ24" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH24" t="n">
+      <c r="AK24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AQ24" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.18</v>
+        <v>3.09</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.65</v>
+        <v>2.57</v>
       </c>
       <c r="R25" t="n">
-        <v>2.99</v>
+        <v>2.59</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>2.12</v>
+        <v>3.78</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV26" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW26" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX26" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA26" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.65</v>
+        <v>1.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>6.36</v>
       </c>
       <c r="R29" t="n">
-        <v>2.55</v>
+        <v>12</v>
       </c>
       <c r="S29" t="n">
-        <v>3.45</v>
+        <v>1.72</v>
       </c>
       <c r="T29" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>2.82</v>
+        <v>9.15</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="X29" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AB29" t="n">
         <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AL29" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BE29" t="n">
         <v>2.01</v>
       </c>
-      <c r="AM29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>4.63</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R30" t="n">
-        <v>1.66</v>
+        <v>5.7</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.36</v>
+        <v>5.6</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="S31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>10.3</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>2.55</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>2.99</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
         <v>7</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD33" t="n">
         <v>3.6</v>
       </c>
-      <c r="BB33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI41" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9514,10 +9514,10 @@
         <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.59</v>
-      </c>
       <c r="BE4" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S5" t="n">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD5" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS14" t="n">
         <v>2.33</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AT14" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT15" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R15" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="S15" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X15" t="n">
+      <c r="AU15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>2.95</v>
       </c>
-      <c r="Y15" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="AW15" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T16" t="n">
         <v>2.06</v>
       </c>
-      <c r="T16" t="n">
-        <v>2.31</v>
-      </c>
       <c r="U16" t="n">
-        <v>5.48</v>
+        <v>4.6</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="X16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC16" t="n">
         <v>2.47</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="BD16" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.47</v>
       </c>
-      <c r="Z16" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA16" t="n">
+      <c r="BF16" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.48</v>
+        <v>1.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>3.62</v>
       </c>
       <c r="R18" t="n">
-        <v>2.65</v>
+        <v>4.24</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
@@ -3998,10 +3998,10 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.98</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.62</v>
+        <v>3.7</v>
       </c>
       <c r="R20" t="n">
-        <v>4.24</v>
+        <v>3.78</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>2.12</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="S24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.36</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X26" t="n">
         <v>3.7</v>
       </c>
-      <c r="R26" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U26" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.41</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AI26" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH26" t="n">
+      <c r="AK26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AQ26" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.19</v>
+        <v>4.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.36</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>12</v>
+        <v>1.66</v>
       </c>
       <c r="S29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>9.15</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.86</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="R30" t="n">
-        <v>5.7</v>
+        <v>10.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
         <v>1.22</v>
       </c>
-      <c r="Q31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>1.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>6.36</v>
       </c>
       <c r="R33" t="n">
-        <v>2.55</v>
+        <v>12</v>
       </c>
       <c r="S33" t="n">
-        <v>3.45</v>
+        <v>1.72</v>
       </c>
       <c r="T33" t="n">
-        <v>2.03</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>2.82</v>
+        <v>9.15</v>
       </c>
       <c r="V33" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.38</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.2</v>
+        <v>4.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.02</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.2</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.26</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" t="n">
-        <v>7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AL33" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>4.85</v>
+      </c>
+      <c r="BE33" t="n">
         <v>2.01</v>
       </c>
-      <c r="AM33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BF33" t="n">
-        <v>1.14</v>
+        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.63</v>
+        <v>1.49</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R35" t="n">
-        <v>1.66</v>
+        <v>5.7</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AQ35" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR35" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS35" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD36" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK36" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AO36" t="n">
         <v>0</v>
       </c>
       <c r="AP36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ36" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR36" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AS36" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV36" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AW36" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AX36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AY36" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AZ36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BA36" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC36" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD36" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE36" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="AJ37" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AK37" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR37" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS37" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU37" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AV37" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AW37" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AX37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AY37" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AZ37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BA37" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="BB37" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="BC37" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="BE37" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="BF37" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="R46" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE46" t="n">
-        <v>1.93</v>
+        <v>3.3</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.81</v>
+        <v>1.29</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>3.33</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV16" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AW16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ16" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>3.33</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="BE17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="BF17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3962,40 +3962,40 @@
         <v>4.24</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AE18" t="n">
         <v>1.98</v>
@@ -4004,28 +4004,28 @@
         <v>1.78</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.7</v>
+        <v>3.22</v>
       </c>
       <c r="R20" t="n">
-        <v>3.78</v>
+        <v>3.24</v>
       </c>
       <c r="S20" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.19</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.58</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR21" t="n">
         <v>1.87</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="R22" t="n">
-        <v>2.12</v>
+        <v>2.59</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AY22" t="n">
         <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,79 +4938,79 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>3.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>1.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
@@ -5052,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R24" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW24" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW24" t="n">
-        <v>0</v>
-      </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.09</v>
+        <v>2.48</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.57</v>
+        <v>3.35</v>
       </c>
       <c r="R25" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>2.88</v>
       </c>
       <c r="T25" t="n">
-        <v>1.58</v>
+        <v>2.11</v>
       </c>
       <c r="U25" t="n">
-        <v>3.68</v>
+        <v>3.45</v>
       </c>
       <c r="V25" t="n">
-        <v>1.85</v>
+        <v>1.33</v>
       </c>
       <c r="W25" t="n">
-        <v>1.85</v>
+        <v>3.16</v>
       </c>
       <c r="X25" t="n">
-        <v>4.6</v>
+        <v>2.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.13</v>
+        <v>1.42</v>
       </c>
       <c r="Z25" t="n">
-        <v>17</v>
+        <v>5.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.82</v>
+        <v>1.22</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.93</v>
+        <v>3.5</v>
       </c>
       <c r="AE25" t="n">
-        <v>3.28</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.25</v>
+        <v>1.92</v>
       </c>
       <c r="AG25" t="n">
-        <v>6.1</v>
+        <v>2.83</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" t="n">
-        <v>15.5</v>
+        <v>5.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.62</v>
+        <v>1.63</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.46</v>
+        <v>2.14</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.47</v>
+        <v>1.29</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.23</v>
+        <v>1.51</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AV25" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY25" t="n">
         <v>0</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BA25" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.49</v>
+        <v>1.18</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.18</v>
+        <v>2</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.36</v>
+        <v>3.94</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.39</v>
+        <v>2.12</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR27" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AV27" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW27" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX27" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BA27" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5932,124 +5932,124 @@
         <v>3.33</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO28" t="n">
         <v>0</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AQ28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AS28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AU28" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AW28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AX28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY28" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="BB28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="BD28" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="BE28" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BF28" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG28" t="n">
         <v>0</v>
@@ -6129,13 +6129,13 @@
         <v>1.66</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6144,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6159,40 +6159,40 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6326,13 +6326,13 @@
         <v>10.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.19</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.36</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="S33" t="n">
-        <v>1.72</v>
+        <v>3.45</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="U33" t="n">
-        <v>9.15</v>
+        <v>2.82</v>
       </c>
       <c r="V33" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="X33" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
-        <v>5.05</v>
+        <v>7</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AB33" t="n">
         <v>1.01</v>
       </c>
       <c r="AC33" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>1.19</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>6.36</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>12</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE34" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK34" t="n">
         <v>2.01</v>
       </c>
-      <c r="AF34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7705,124 +7705,124 @@
         <v>4.25</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK37" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AL37" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO37" t="n">
         <v>0</v>
       </c>
       <c r="AP37" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AR37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AS37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AU37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV37" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AW37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AX37" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AY37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BA37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BB37" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="BC37" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BD37" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BE37" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF37" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8296,124 +8296,124 @@
         <v>3.38</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>4.13</v>
       </c>
       <c r="AH40" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI40" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK40" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AO40" t="n">
         <v>0</v>
       </c>
       <c r="AP40" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AR40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AU40" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AV40" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW40" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AX40" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AY40" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BA40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="BB40" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC40" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BD40" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="BE40" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="BF40" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG40" t="n">
         <v>0</v>
@@ -8493,40 +8493,40 @@
         <v>2.95</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE41" t="n">
         <v>1.93</v>
@@ -8535,28 +8535,28 @@
         <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL41" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC41" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD41" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE41" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF41" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AF42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.93</v>
       </c>
-      <c r="AG42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
       <c r="AL42" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC42" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD42" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BE42" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF42" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9547,40 +9547,40 @@
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB46" t="n">
         <v>1.49</v>
@@ -9675,124 +9675,124 @@
         <v>3.35</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U47" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD47" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG47" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI47" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK47" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AL47" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO47" t="n">
         <v>0</v>
       </c>
       <c r="AP47" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AR47" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AS47" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AT47" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="AU47" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AX47" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AY47" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BA47" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BB47" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD47" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE47" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF47" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG47" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD5" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>2.59</v>
-      </c>
       <c r="BE5" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S14" t="n">
-        <v>4.3</v>
+        <v>2.33</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U14" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AK14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA14" t="n">
         <v>2.85</v>
       </c>
-      <c r="AE14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="BB14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC14" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>4.97</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="U15" t="n">
-        <v>5.48</v>
+        <v>2.72</v>
       </c>
       <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM15" t="n">
         <v>1.31</v>
       </c>
-      <c r="W15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF15" t="n">
+      <c r="AN15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>2.04</v>
       </c>
-      <c r="AG15" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ15" t="n">
+      <c r="BA15" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF15" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>4.97</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AO16" t="n">
         <v>0</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AX16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AY16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BD16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BF16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,37 +3756,37 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.33</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.33</v>
+        <v>3.46</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>3.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="X17" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>1.02</v>
@@ -3795,91 +3795,91 @@
         <v>1.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI17" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AN17" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="AO17" t="n">
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF17" t="n">
         <v>1.08</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>3.24</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4461,19 +4461,19 @@
         <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>2.48</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="R21" t="n">
-        <v>3.78</v>
+        <v>2.65</v>
       </c>
       <c r="S21" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="U21" t="n">
-        <v>4.49</v>
+        <v>3.45</v>
       </c>
       <c r="V21" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="W21" t="n">
-        <v>3.35</v>
+        <v>3.16</v>
       </c>
       <c r="X21" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.56</v>
+        <v>2.83</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" t="n">
-        <v>4.75</v>
+        <v>5.2</v>
       </c>
       <c r="AJ21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB21" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.14</v>
-      </c>
       <c r="BC21" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.6</v>
+        <v>3.94</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="R22" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X22" t="n">
         <v>2.59</v>
       </c>
-      <c r="S22" t="n">
-        <v>5</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR22" t="n">
         <v>1.85</v>
       </c>
-      <c r="W22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X22" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ22" t="n">
+      <c r="AS22" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW22" t="n">
         <v>1.83</v>
       </c>
-      <c r="AR22" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AX22" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BA22" t="n">
         <v>1.89</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="BC22" t="n">
-        <v>3.18</v>
+        <v>1.95</v>
       </c>
       <c r="BD22" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.58</v>
+        <v>3.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>2.57</v>
       </c>
       <c r="R23" t="n">
-        <v>1.87</v>
+        <v>2.59</v>
       </c>
       <c r="S23" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>3.68</v>
       </c>
       <c r="V23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X23" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.28</v>
       </c>
-      <c r="W23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.81</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W24" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X24" t="n">
         <v>2.39</v>
       </c>
-      <c r="S24" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U24" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W24" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X24" t="n">
-        <v>2.59</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.78</v>
+        <v>4.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.16</v>
+        <v>4.65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="AU24" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.48</v>
+        <v>2.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.35</v>
+        <v>2.61</v>
       </c>
       <c r="R25" t="n">
-        <v>2.65</v>
+        <v>2.97</v>
       </c>
       <c r="S25" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.11</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="V25" t="n">
-        <v>1.33</v>
+        <v>1.61</v>
       </c>
       <c r="W25" t="n">
-        <v>3.16</v>
+        <v>2.25</v>
       </c>
       <c r="X25" t="n">
-        <v>2.62</v>
+        <v>3.7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.42</v>
+        <v>1.18</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AD25" t="n">
-        <v>3.5</v>
+        <v>2.27</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.92</v>
+        <v>1.36</v>
       </c>
       <c r="AG25" t="n">
-        <v>2.83</v>
+        <v>5.55</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AI25" t="n">
-        <v>5.2</v>
+        <v>12.5</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.63</v>
+        <v>2.15</v>
       </c>
       <c r="AL25" t="n">
-        <v>2.14</v>
+        <v>1.57</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.18</v>
+        <v>1.38</v>
       </c>
       <c r="BC25" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="BD25" t="n">
-        <v>3.94</v>
+        <v>2.77</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.78</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.61</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>2.97</v>
+        <v>3.78</v>
       </c>
       <c r="S26" t="n">
-        <v>2.99</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>4.33</v>
+        <v>4.49</v>
       </c>
       <c r="V26" t="n">
-        <v>1.61</v>
+        <v>1.27</v>
       </c>
       <c r="W26" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="X26" t="n">
-        <v>3.7</v>
+        <v>2.41</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z26" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK26" t="n">
-        <v>2.15</v>
+        <v>1.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>1.57</v>
+        <v>2.18</v>
       </c>
       <c r="AM26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>1.35</v>
       </c>
-      <c r="AN26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AR26" t="n">
-        <v>2.07</v>
+        <v>1.87</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.7</v>
+        <v>2.06</v>
       </c>
       <c r="AT26" t="n">
-        <v>3.6</v>
+        <v>2.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.05</v>
+        <v>2.74</v>
       </c>
       <c r="AW26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX26" t="n">
         <v>1.66</v>
       </c>
-      <c r="AX26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AY26" t="n">
-        <v>1.24</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.77</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.63</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="R29" t="n">
-        <v>1.66</v>
+        <v>5.7</v>
       </c>
       <c r="S29" t="n">
-        <v>4.6</v>
+        <v>2.1</v>
       </c>
       <c r="T29" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="U29" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X29" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="Y29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ29" t="n">
         <v>1.45</v>
       </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ29" t="n">
+      <c r="AR29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF29" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC29" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BF29" t="n">
-        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,22 +6317,22 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="R30" t="n">
-        <v>10.3</v>
+        <v>2.65</v>
       </c>
       <c r="S30" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
         <v>0</v>
@@ -6341,10 +6341,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -6356,40 +6356,40 @@
         <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.42</v>
+        <v>2.01</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6434,13 +6434,13 @@
         <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
         <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>4.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R32" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG32" t="n">
         <v>2.65</v>
       </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>0</v>
-      </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>2.65</v>
+        <v>1.22</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>5.6</v>
       </c>
       <c r="R33" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U33" t="n">
+        <v>7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF33" t="n">
         <v>2.55</v>
       </c>
-      <c r="S33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AG33" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.26</v>
+        <v>1.63</v>
       </c>
       <c r="AI33" t="n">
-        <v>7</v>
+        <v>3.35</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.01</v>
+        <v>1.85</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.25</v>
+        <v>1.04</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.41</v>
+        <v>3.15</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.16</v>
+        <v>1.63</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R35" t="n">
-        <v>5.7</v>
+        <v>2.55</v>
       </c>
       <c r="S35" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="T35" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="V35" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W35" t="n">
-        <v>2.56</v>
+        <v>2.99</v>
       </c>
       <c r="X35" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z35" t="n">
         <v>7</v>
       </c>
       <c r="AA35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB35" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB35" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC35" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI35" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AJ35" t="n">
         <v>1.06</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS35" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW35" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX35" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ35" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD35" t="n">
         <v>3.6</v>
       </c>
-      <c r="BB35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BE35" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U36" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V36" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="W36" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="X36" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.38</v>
+        <v>2.09</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>3.04</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.39</v>
+        <v>6.55</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI36" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S37" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR37" t="n">
         <v>1.85</v>
       </c>
-      <c r="U37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="AS37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8099,46 +8099,46 @@
         <v>21</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AG39" t="n">
         <v>1.93</v>
@@ -8147,76 +8147,76 @@
         <v>1.93</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AK39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AM39" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AN39" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AO39" t="n">
         <v>0</v>
       </c>
       <c r="AP39" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AQ39" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AR39" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AS39" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AU39" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AV39" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AW39" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="AX39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AY39" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA39" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BB39" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC39" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BD39" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE39" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF39" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BG39" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.95</v>
+        <v>3.2</v>
       </c>
       <c r="S41" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="T41" t="n">
-        <v>2.08</v>
+        <v>1.85</v>
       </c>
       <c r="U41" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="V41" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="W41" t="n">
-        <v>2.82</v>
+        <v>2.34</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="Y41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC41" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z41" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.23</v>
-      </c>
       <c r="AD41" t="n">
-        <v>3.42</v>
+        <v>2.62</v>
       </c>
       <c r="AE41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK41" t="n">
         <v>1.93</v>
       </c>
-      <c r="AF41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH41" t="n">
+      <c r="AL41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB41" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI41" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ41" t="n">
+      <c r="BC41" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF41" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC41" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD41" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="BE41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF41" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>3.44</v>
       </c>
       <c r="R42" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T42" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>4.24</v>
+        <v>4.26</v>
       </c>
       <c r="V42" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="X42" t="n">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA42" t="n">
         <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.62</v>
+        <v>3.34</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AI42" t="n">
-        <v>9.1</v>
+        <v>5.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.93</v>
+        <v>1.71</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.31</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>5.95</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI45" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK45" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL45" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>4.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>5.96</v>
+        <v>6.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.94</v>
+        <v>5.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.9</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.59</v>
-      </c>
       <c r="BE4" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
-        <v>4.13</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>5.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE5" t="n">
         <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q14" t="n">
         <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S14" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS14" t="n">
         <v>2.33</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U14" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AT14" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AU14" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AV14" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AW14" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AX14" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AY14" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>3.46</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>2.72</v>
+        <v>3.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="X15" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.31</v>
+        <v>1.39</v>
       </c>
       <c r="AN15" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,37 +3756,37 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>3.33</v>
       </c>
       <c r="S17" t="n">
-        <v>3.46</v>
+        <v>2.33</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="U17" t="n">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA17" t="n">
         <v>1.02</v>
@@ -3795,91 +3795,91 @@
         <v>1.07</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AJ17" t="n">
         <v>1.02</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AN17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.41</v>
       </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV17" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW17" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY17" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BD17" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF17" t="n">
         <v>1.08</v>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R18" t="n">
-        <v>4.24</v>
+        <v>3.24</v>
       </c>
       <c r="S18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>3.15</v>
       </c>
       <c r="Q19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W19" t="n">
         <v>3.22</v>
       </c>
-      <c r="R19" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.33</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.58</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>1.87</v>
+        <v>2.65</v>
       </c>
       <c r="S20" t="n">
-        <v>4.45</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>3.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="X20" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.18</v>
       </c>
-      <c r="AD20" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.16</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,130 +4544,130 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="S21" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="T21" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U21" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="V21" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W21" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="X21" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z21" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB21" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AE21" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW21" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>0</v>
-      </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="BC21" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BF21" t="n">
         <v>1.18</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="R22" t="n">
-        <v>2.39</v>
+        <v>2.97</v>
       </c>
       <c r="S22" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="T22" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="U22" t="n">
-        <v>2.78</v>
+        <v>4.33</v>
       </c>
       <c r="V22" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM22" t="n">
         <v>1.35</v>
       </c>
-      <c r="W22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AN22" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.36</v>
       </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.09</v>
+        <v>3.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.57</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S23" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG23" t="n">
         <v>2.59</v>
       </c>
-      <c r="S23" t="n">
-        <v>5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U23" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X23" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>6.1</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>15.5</v>
+        <v>4.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL23" t="n">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
         <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="BC23" t="n">
-        <v>3.18</v>
+        <v>1.92</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.28</v>
+        <v>1.81</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.78</v>
+        <v>1.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.61</v>
+        <v>3.62</v>
       </c>
       <c r="R25" t="n">
-        <v>2.97</v>
+        <v>4.24</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>2.13</v>
       </c>
       <c r="U25" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V25" t="n">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="W25" t="n">
-        <v>2.25</v>
+        <v>2.85</v>
       </c>
       <c r="X25" t="n">
-        <v>3.7</v>
+        <v>2.81</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="Z25" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AC25" t="n">
-        <v>1.57</v>
+        <v>1.28</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.27</v>
+        <v>3.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.75</v>
+        <v>1.98</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>5.55</v>
+        <v>3.2</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AI25" t="n">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AJ25" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AK25" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AL25" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.67</v>
       </c>
-      <c r="AR25" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.36</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.03</v>
+        <v>1.17</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="R26" t="n">
-        <v>3.78</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>4.49</v>
+        <v>3.68</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="W26" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="X26" t="n">
-        <v>2.41</v>
+        <v>4.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AI26" t="n">
-        <v>4.75</v>
+        <v>15.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AN26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
         <v>2.06</v>
       </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BA26" t="n">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>3.18</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>2.36</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R27" t="n">
-        <v>2.12</v>
+        <v>3.78</v>
       </c>
       <c r="S27" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="T27" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U27" t="n">
-        <v>2.35</v>
+        <v>4.49</v>
       </c>
       <c r="V27" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W27" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="X27" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA27" t="n">
         <v>1.08</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AH27" t="n">
         <v>1.4</v>
       </c>
       <c r="AI27" t="n">
-        <v>5.33</v>
+        <v>4.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AR27" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AS27" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AT27" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="AU27" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="AV27" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AW27" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.66</v>
+        <v>2.66</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.7</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R30" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U30" t="n">
+        <v>6</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU30" t="n">
         <v>3.4</v>
       </c>
-      <c r="R30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6559,10 +6559,10 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,35 +6711,35 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>4.63</v>
+        <v>1.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.7</v>
+        <v>5.6</v>
       </c>
       <c r="R32" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="U32" t="n">
+        <v>7</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y32" t="n">
         <v>1.66</v>
       </c>
-      <c r="S32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U32" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.45</v>
-      </c>
       <c r="Z32" t="n">
         <v>0</v>
       </c>
@@ -6750,91 +6750,91 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AD32" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AF32" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="BD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE32" t="n">
         <v>2</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="BD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE32" t="n">
-        <v>1.75</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.6</v>
+        <v>6.36</v>
       </c>
       <c r="R33" t="n">
-        <v>10.3</v>
+        <v>12</v>
       </c>
       <c r="S33" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="T33" t="n">
-        <v>2.88</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>7</v>
+        <v>9.15</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>1.97</v>
+        <v>2.31</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.66</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>5</v>
+        <v>4.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.63</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" t="n">
-        <v>3.35</v>
+        <v>3.86</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.04</v>
+        <v>1.13</v>
       </c>
       <c r="AN33" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE33" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.19</v>
+        <v>2.65</v>
       </c>
       <c r="Q34" t="n">
-        <v>6.36</v>
+        <v>3.2</v>
       </c>
       <c r="R34" t="n">
-        <v>12</v>
+        <v>2.55</v>
       </c>
       <c r="S34" t="n">
-        <v>1.72</v>
+        <v>3.45</v>
       </c>
       <c r="T34" t="n">
-        <v>2.44</v>
+        <v>2.03</v>
       </c>
       <c r="U34" t="n">
-        <v>9.15</v>
+        <v>2.82</v>
       </c>
       <c r="V34" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W34" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="X34" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.53</v>
+        <v>1.38</v>
       </c>
       <c r="Z34" t="n">
-        <v>5.05</v>
+        <v>7</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AB34" t="n">
         <v>1.01</v>
       </c>
       <c r="AC34" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD34" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BF34" t="n">
         <v>1.14</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB34" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC34" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD34" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF34" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG35" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R35" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S35" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T35" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U35" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W35" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y35" t="n">
+      <c r="AH35" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE35" t="n">
+      <c r="AI35" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL35" t="n">
         <v>2.02</v>
       </c>
-      <c r="AF35" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AM35" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="BD35" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R41" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T41" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="U41" t="n">
-        <v>4.24</v>
+        <v>4.31</v>
       </c>
       <c r="V41" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W41" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="X41" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI41" t="n">
-        <v>9.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8598,19 +8598,19 @@
         <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="S42" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="U42" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W42" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="X42" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="AA42" t="n">
         <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AF42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.93</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AL42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD42" t="n">
         <v>3.14</v>
       </c>
-      <c r="AH42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>3.82</v>
-      </c>
       <c r="BE42" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="R44" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="S44" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X44" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA44" t="n">
         <v>2.55</v>
       </c>
-      <c r="T44" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U44" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>0</v>
-      </c>
       <c r="BB44" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.92</v>
+        <v>2.36</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK45" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC45" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD45" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF45" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,133 +9469,133 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.67</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.51</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>2.97</v>
+        <v>3.6</v>
       </c>
       <c r="S46" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="T46" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="U46" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
-        <v>1.79</v>
+        <v>1.49</v>
       </c>
       <c r="W46" t="n">
-        <v>1.9</v>
+        <v>2.34</v>
       </c>
       <c r="X46" t="n">
-        <v>4.6</v>
+        <v>3.34</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.75</v>
+        <v>1.38</v>
       </c>
       <c r="AD46" t="n">
-        <v>1.93</v>
+        <v>2.62</v>
       </c>
       <c r="AE46" t="n">
-        <v>3.3</v>
+        <v>2.29</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.29</v>
+        <v>1.54</v>
       </c>
       <c r="AG46" t="n">
-        <v>7.5</v>
+        <v>4.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AI46" t="n">
-        <v>19</v>
+        <v>9.1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
       </c>
       <c r="AP46" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
       <c r="AU46" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
         <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="BC46" t="n">
-        <v>3.3</v>
+        <v>2.41</v>
       </c>
       <c r="BD46" t="n">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>4.71</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8</v>
+        <v>5.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.9</v>
+        <v>3.94</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>7.9</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AS3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.45</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.91</v>
-      </c>
       <c r="BD3" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>4.13</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>5.96</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AE5" t="n">
         <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.22</v>
+        <v>2.61</v>
       </c>
       <c r="R18" t="n">
-        <v>3.24</v>
+        <v>2.97</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AS18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AV18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AW18" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AY18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>3.58</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="R20" t="n">
-        <v>2.65</v>
+        <v>1.87</v>
       </c>
       <c r="S20" t="n">
-        <v>2.88</v>
+        <v>4.45</v>
       </c>
       <c r="T20" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="U20" t="n">
-        <v>3.45</v>
+        <v>2.22</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W20" t="n">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="X20" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="AF20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC20" t="n">
         <v>1.92</v>
       </c>
-      <c r="AG20" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>2</v>
-      </c>
       <c r="BD20" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.65</v>
+        <v>1.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>3.62</v>
       </c>
       <c r="R21" t="n">
-        <v>2.39</v>
+        <v>4.24</v>
       </c>
       <c r="S21" t="n">
-        <v>3.82</v>
+        <v>2.31</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="U21" t="n">
-        <v>2.78</v>
+        <v>4.5</v>
       </c>
       <c r="V21" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W21" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="X21" t="n">
-        <v>2.59</v>
+        <v>2.81</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>7.2</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.05</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AK21" t="n">
-        <v>1.56</v>
+        <v>1.8</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.19</v>
+        <v>1.9</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.36</v>
+        <v>2</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AU21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AW21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.25</v>
+        <v>3.84</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="R22" t="n">
-        <v>2.97</v>
+        <v>2.65</v>
       </c>
       <c r="S22" t="n">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="T22" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U22" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W22" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>2</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="BE22" t="n">
         <v>1.75</v>
       </c>
-      <c r="U22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="BF22" t="n">
         <v>1.18</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="BC22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="BE22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BF22" t="n">
-        <v>1.03</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,130 +4938,130 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.58</v>
+        <v>2.18</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>3.65</v>
       </c>
       <c r="R23" t="n">
-        <v>1.87</v>
+        <v>2.99</v>
       </c>
       <c r="S23" t="n">
-        <v>4.45</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>3.43</v>
       </c>
       <c r="V23" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>3.28</v>
+        <v>3.48</v>
       </c>
       <c r="X23" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB23" t="n">
         <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.92</v>
+        <v>4.35</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.12</v>
+        <v>2.23</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="AJ23" t="n">
         <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.66</v>
+        <v>1.55</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.79</v>
+        <v>1.23</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.19</v>
+        <v>1.67</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="BF23" t="n">
         <v>1.21</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>2.99</v>
+        <v>3.24</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.43</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.78</v>
+        <v>3.09</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.62</v>
+        <v>2.57</v>
       </c>
       <c r="R25" t="n">
-        <v>4.24</v>
+        <v>2.59</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>5</v>
       </c>
       <c r="T25" t="n">
-        <v>2.13</v>
+        <v>1.58</v>
       </c>
       <c r="U25" t="n">
-        <v>4.5</v>
+        <v>3.68</v>
       </c>
       <c r="V25" t="n">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="W25" t="n">
-        <v>2.85</v>
+        <v>1.85</v>
       </c>
       <c r="X25" t="n">
-        <v>2.81</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.37</v>
+        <v>1.13</v>
       </c>
       <c r="Z25" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AJ25" t="n">
         <v>1.01</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AK25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.28</v>
       </c>
-      <c r="AD25" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.59</v>
       </c>
-      <c r="S26" t="n">
-        <v>5</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U26" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR26" t="n">
         <v>1.85</v>
       </c>
-      <c r="W26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ26" t="n">
+      <c r="AS26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW26" t="n">
         <v>1.83</v>
       </c>
-      <c r="AR26" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AX26" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AY26" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BA26" t="n">
         <v>1.89</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="BC26" t="n">
-        <v>3.18</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,22 +6120,22 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>4.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
         <v>0</v>
@@ -6144,10 +6144,10 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -6159,40 +6159,40 @@
         <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6237,13 +6237,13 @@
         <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD29" t="n">
         <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF29" t="n">
         <v>0</v>
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R30" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S30" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T30" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U30" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V30" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W30" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X30" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC30" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD30" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI30" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="R31" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL31" t="n">
         <v>2.01</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.36</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="S33" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U33" t="n">
-        <v>9.15</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>1.3</v>
       </c>
-      <c r="W33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="BC33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,79 +7105,79 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7219,19 +7219,19 @@
         <v>0</v>
       </c>
       <c r="BB34" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,22 +7302,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R35" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="S35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7326,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -7341,40 +7341,40 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7419,13 +7419,13 @@
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR36" t="n">
         <v>1.85</v>
       </c>
-      <c r="U36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AS36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="W37" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="X37" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.38</v>
+        <v>2.09</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>3.04</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.39</v>
+        <v>6.55</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI37" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R41" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="S41" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="T41" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U41" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="V41" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W41" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="X41" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z41" t="n">
-        <v>6.95</v>
+        <v>7.2</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD41" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AE41" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF41" t="n">
         <v>1.93</v>
       </c>
-      <c r="AF41" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG41" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI41" t="n">
-        <v>5.95</v>
+        <v>5.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AL41" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8601,13 +8601,13 @@
         <v>1.18</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BF41" t="n">
         <v>1.14</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AQ43" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AR43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AS43" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AV43" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AW43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AX43" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.67</v>
+        <v>2.21</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.51</v>
+        <v>3.25</v>
       </c>
       <c r="R44" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="T44" t="n">
-        <v>1.75</v>
+        <v>2.08</v>
       </c>
       <c r="U44" t="n">
-        <v>3.8</v>
+        <v>4.31</v>
       </c>
       <c r="V44" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="W44" t="n">
-        <v>1.9</v>
+        <v>2.82</v>
       </c>
       <c r="X44" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.13</v>
+        <v>1.38</v>
       </c>
       <c r="Z44" t="n">
-        <v>17</v>
+        <v>6.95</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB44" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC44" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AQ44" t="n">
+      <c r="BC44" t="n">
         <v>2.04</v>
       </c>
-      <c r="AR44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>3.3</v>
-      </c>
       <c r="BD44" t="n">
-        <v>2.36</v>
+        <v>3.92</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.3</v>
+        <v>1.69</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.44</v>
+        <v>2.95</v>
       </c>
       <c r="R45" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="S45" t="n">
         <v>2.66</v>
       </c>
       <c r="T45" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="U45" t="n">
-        <v>4.26</v>
+        <v>5</v>
       </c>
       <c r="V45" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X45" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.38</v>
       </c>
-      <c r="W45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AD45" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.93</v>
+        <v>1.54</v>
       </c>
       <c r="AG45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD45" t="n">
         <v>3.14</v>
       </c>
-      <c r="AH45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC45" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD45" t="n">
-        <v>3.82</v>
-      </c>
       <c r="BE45" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AG46" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AI46" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9583,19 +9583,19 @@
         <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>4.13</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>5.96</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
         <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
         <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
-        <v>4.13</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>5.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE5" t="n">
         <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,37 +3362,37 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>3.33</v>
       </c>
       <c r="S15" t="n">
-        <v>3.46</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>3.62</v>
+        <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>2.51</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>8.300000000000001</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
         <v>1.02</v>
@@ -3401,91 +3401,91 @@
         <v>1.07</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.49</v>
+        <v>2.62</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="AG15" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="AJ15" t="n">
         <v>1.02</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.95</v>
+        <v>2.08</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.39</v>
+        <v>1.28</v>
       </c>
       <c r="AN15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.41</v>
       </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AU15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AX15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.99</v>
+        <v>3.16</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF15" t="n">
         <v>1.08</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>2.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R16" t="n">
-        <v>4.97</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>2.06</v>
+        <v>3.46</v>
       </c>
       <c r="T16" t="n">
-        <v>2.31</v>
+        <v>1.83</v>
       </c>
       <c r="U16" t="n">
-        <v>5.48</v>
+        <v>3.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
-        <v>3.1</v>
+        <v>2.51</v>
       </c>
       <c r="X16" t="n">
-        <v>2.47</v>
+        <v>3.22</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>5.55</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>3.33</v>
+        <v>4.97</v>
       </c>
       <c r="S17" t="n">
-        <v>2.33</v>
+        <v>2.06</v>
       </c>
       <c r="T17" t="n">
-        <v>2.06</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>4.6</v>
+        <v>5.48</v>
       </c>
       <c r="V17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y17" t="n">
         <v>1.47</v>
       </c>
-      <c r="W17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ17" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG17" t="n">
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD17" t="n">
         <v>4.05</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>3.16</v>
-      </c>
       <c r="BE17" t="n">
-        <v>1.47</v>
+        <v>1.76</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.78</v>
+        <v>3.58</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.61</v>
+        <v>3.85</v>
       </c>
       <c r="R18" t="n">
-        <v>2.97</v>
+        <v>1.87</v>
       </c>
       <c r="S18" t="n">
-        <v>2.99</v>
+        <v>4.45</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>4.33</v>
+        <v>2.22</v>
       </c>
       <c r="V18" t="n">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="W18" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7</v>
+        <v>2.44</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC18" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z18" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AD18" t="n">
-        <v>2.27</v>
+        <v>3.92</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.75</v>
+        <v>1.68</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="AG18" t="n">
-        <v>5.55</v>
+        <v>2.59</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="AI18" t="n">
-        <v>12.5</v>
+        <v>4.62</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AK18" t="n">
-        <v>2.15</v>
+        <v>1.66</v>
       </c>
       <c r="AL18" t="n">
-        <v>1.57</v>
+        <v>2.09</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.58</v>
+        <v>1.19</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.38</v>
+        <v>1.16</v>
       </c>
       <c r="BC18" t="n">
-        <v>2.8</v>
+        <v>1.92</v>
       </c>
       <c r="BD18" t="n">
-        <v>2.77</v>
+        <v>4.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.36</v>
+        <v>1.81</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="S19" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="V19" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="X19" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="AJ19" t="n">
         <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="R20" t="n">
-        <v>1.87</v>
+        <v>2.97</v>
       </c>
       <c r="S20" t="n">
-        <v>4.45</v>
+        <v>2.99</v>
       </c>
       <c r="T20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="U20" t="n">
-        <v>2.22</v>
+        <v>4.33</v>
       </c>
       <c r="V20" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="W20" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="X20" t="n">
-        <v>2.44</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.92</v>
+        <v>2.27</v>
       </c>
       <c r="AE20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>1.68</v>
       </c>
-      <c r="AF20" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>4.62</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>0</v>
-      </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="BC20" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>4.25</v>
+        <v>2.77</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>4.24</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT21" t="n">
         <v>2.31</v>
       </c>
-      <c r="T21" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AU21" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AV21" t="n">
         <v>3.2</v>
       </c>
-      <c r="AH21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>0</v>
-      </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.02</v>
+        <v>1.96</v>
       </c>
       <c r="BD21" t="n">
-        <v>3.84</v>
+        <v>4.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q22" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R22" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W22" t="n">
         <v>3.35</v>
       </c>
-      <c r="R22" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.16</v>
-      </c>
       <c r="X22" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB22" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI22" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BC22" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.18</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>2.99</v>
+        <v>4.24</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>2.36</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>3.43</v>
+        <v>4.5</v>
       </c>
       <c r="V23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.26</v>
       </c>
-      <c r="W23" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AI23" t="n">
-        <v>4.65</v>
+        <v>6.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BD23" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="BE23" t="n">
         <v>1.67</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>1.87</v>
-      </c>
       <c r="BF23" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>3.09</v>
+        <v>2.65</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.57</v>
+        <v>3.4</v>
       </c>
       <c r="R25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X25" t="n">
         <v>2.59</v>
       </c>
-      <c r="S25" t="n">
-        <v>5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U25" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR25" t="n">
         <v>1.85</v>
       </c>
-      <c r="W25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X25" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN25" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ25" t="n">
+      <c r="AS25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW25" t="n">
         <v>1.83</v>
       </c>
-      <c r="AR25" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.52</v>
-      </c>
       <c r="AX25" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
       <c r="AY25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AZ25" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BA25" t="n">
         <v>1.89</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="BC25" t="n">
-        <v>3.18</v>
+        <v>1.95</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.28</v>
+        <v>1.78</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="R26" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X26" t="n">
         <v>2.39</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="U26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.59</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.43</v>
+        <v>1.51</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>3.78</v>
+        <v>4.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AI26" t="n">
-        <v>5.16</v>
+        <v>4.65</v>
       </c>
       <c r="AJ26" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="AL26" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
       </c>
       <c r="AP26" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AQ26" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AR26" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.23</v>
+        <v>1.84</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.9</v>
+        <v>2.31</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.25</v>
+        <v>4.75</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.4</v>
+        <v>3.05</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.56</v>
+        <v>1.84</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.89</v>
+        <v>2.58</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.25</v>
+        <v>4.65</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.78</v>
+        <v>1.87</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>1.9</v>
+        <v>3.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.7</v>
+        <v>2.57</v>
       </c>
       <c r="R27" t="n">
-        <v>3.78</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
-        <v>2.2</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>1.58</v>
       </c>
       <c r="U27" t="n">
-        <v>4.49</v>
+        <v>3.68</v>
       </c>
       <c r="V27" t="n">
-        <v>1.27</v>
+        <v>1.85</v>
       </c>
       <c r="W27" t="n">
-        <v>3.35</v>
+        <v>1.85</v>
       </c>
       <c r="X27" t="n">
-        <v>2.41</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.53</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.7</v>
+        <v>17</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.4</v>
-      </c>
       <c r="AI27" t="n">
-        <v>4.75</v>
+        <v>15.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.62</v>
+        <v>2.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="AN27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
         <v>2.06</v>
       </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BA27" t="n">
-        <v>2.66</v>
+        <v>1.89</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.14</v>
+        <v>1.49</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.8</v>
+        <v>3.18</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.6</v>
+        <v>2.36</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.86</v>
+        <v>1.28</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.63</v>
+        <v>2.65</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.66</v>
+        <v>2.55</v>
       </c>
       <c r="S29" t="n">
-        <v>4.6</v>
+        <v>3.45</v>
       </c>
       <c r="T29" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="U29" t="n">
-        <v>2.12</v>
+        <v>2.82</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X29" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="AE29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
         <v>1.67</v>
       </c>
-      <c r="AF29" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AL29" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Q30" t="n">
-        <v>6.36</v>
+        <v>5.6</v>
       </c>
       <c r="R30" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="S30" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="T30" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U30" t="n">
-        <v>9.15</v>
+        <v>7</v>
       </c>
       <c r="V30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Z30" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD30" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AG30" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK30" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AL30" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="BD30" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U31" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W31" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="AH31" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE31" t="n">
+      <c r="AI31" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL31" t="n">
         <v>2.02</v>
       </c>
-      <c r="AF31" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AM31" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z33" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R35" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U35" t="n">
+        <v>6</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU35" t="n">
         <v>3.4</v>
       </c>
-      <c r="R35" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
       <c r="AV35" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW35" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC35" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.87</v>
+        <v>2.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.44</v>
+        <v>2.51</v>
       </c>
       <c r="R41" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="S41" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="U41" t="n">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="V41" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="W41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR41" t="n">
         <v>2.7</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
       <c r="AS41" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
       <c r="AU41" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AW41" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AX41" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AY41" t="n">
         <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.82</v>
+        <v>2.36</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="R42" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="S42" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="T42" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="U42" t="n">
-        <v>4.24</v>
+        <v>4.31</v>
       </c>
       <c r="V42" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W42" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="X42" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z42" t="n">
-        <v>9.5</v>
+        <v>6.95</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AD42" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="AE42" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG42" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI42" t="n">
-        <v>9.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AL42" t="n">
-        <v>1.75</v>
+        <v>2.03</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8795,19 +8795,19 @@
         <v>0</v>
       </c>
       <c r="BB42" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,133 +8878,133 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AQ43" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AR43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AS43" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
       <c r="AU43" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AY43" t="n">
         <v>0</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="BA43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,133 +9075,133 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.21</v>
+        <v>1.95</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R44" t="n">
-        <v>2.95</v>
+        <v>3.6</v>
       </c>
       <c r="S44" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="U44" t="n">
+        <v>5</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W44" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X44" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>10</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>2</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BA44" t="n">
         <v>2.55</v>
       </c>
-      <c r="T44" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U44" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W44" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X44" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH44" t="n">
+      <c r="BB44" t="n">
         <v>1.28</v>
       </c>
-      <c r="AI44" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ44" t="n">
+      <c r="BC44" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF44" t="n">
         <v>1.07</v>
-      </c>
-      <c r="AK44" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL44" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AM44" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN44" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB44" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC44" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BD44" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="BE44" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="BF44" t="n">
-        <v>1.14</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,79 +9272,79 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="S45" t="n">
         <v>2.66</v>
       </c>
       <c r="T45" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U45" t="n">
-        <v>5</v>
+        <v>4.26</v>
       </c>
       <c r="V45" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="X45" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD45" t="n">
         <v>3.34</v>
       </c>
-      <c r="Y45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE45" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AG45" t="n">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH45" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AI45" t="n">
-        <v>9.1</v>
+        <v>5.2</v>
       </c>
       <c r="AJ45" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AK45" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AL45" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AO45" t="n">
         <v>0</v>
@@ -9386,19 +9386,19 @@
         <v>0</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD46" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE46" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL46" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9553,13 +9553,13 @@
         <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS46" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT46" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
@@ -9568,34 +9568,34 @@
         <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX46" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AY46" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA46" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB46" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC46" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD46" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BE46" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF46" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
-        <v>4.13</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>5.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
         <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE3" t="n">
         <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AN3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.59</v>
-      </c>
       <c r="BE4" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>4.71</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U5" t="n">
-        <v>5.96</v>
+        <v>6.8</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="X5" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.94</v>
+        <v>5.9</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.9</v>
+        <v>13</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BA5" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4</v>
+      </c>
+      <c r="R14" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U14" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT14" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="R14" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="S14" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="T14" t="n">
-        <v>2</v>
-      </c>
-      <c r="U14" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="X14" t="n">
+      <c r="AU14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV14" t="n">
         <v>2.95</v>
       </c>
-      <c r="Y14" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
+      <c r="AW14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>2.04</v>
-      </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.33</v>
+        <v>1.98</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.36</v>
+        <v>4.05</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.52</v>
+        <v>1.76</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS15" t="n">
         <v>2.33</v>
       </c>
-      <c r="T15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AT15" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T17" t="n">
         <v>2.06</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.31</v>
-      </c>
       <c r="U17" t="n">
-        <v>5.48</v>
+        <v>4.6</v>
       </c>
       <c r="V17" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W17" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="X17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC17" t="n">
         <v>2.47</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="BD17" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.47</v>
       </c>
-      <c r="Z17" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA17" t="n">
+      <c r="BF17" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="Q18" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R18" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="S18" t="n">
         <v>3.85</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.45</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U18" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="V18" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W18" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="X18" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="Z18" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.92</v>
+        <v>3.84</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.59</v>
+        <v>2.72</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>4.62</v>
+        <v>5.33</v>
       </c>
       <c r="AJ18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
         <v>1.12</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AQ18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA18" t="n">
         <v>1.66</v>
       </c>
-      <c r="AL18" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>0</v>
-      </c>
       <c r="BB18" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="BD18" t="n">
         <v>4.25</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="R19" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="R20" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="S20" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="T20" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="U20" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="V20" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="W20" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="X20" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z20" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>5.55</v>
+        <v>6.1</v>
       </c>
       <c r="AH20" t="n">
         <v>1.08</v>
       </c>
       <c r="AI20" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK20" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AW20" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AX20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AY20" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="BA20" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>3.15</v>
+        <v>1.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="R21" t="n">
-        <v>2.12</v>
+        <v>3.78</v>
       </c>
       <c r="S21" t="n">
-        <v>3.85</v>
+        <v>2.2</v>
       </c>
       <c r="T21" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="U21" t="n">
-        <v>2.35</v>
+        <v>4.49</v>
       </c>
       <c r="V21" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="W21" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="X21" t="n">
-        <v>2.53</v>
+        <v>2.41</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="Z21" t="n">
-        <v>6.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA21" t="n">
         <v>1.08</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AD21" t="n">
-        <v>3.84</v>
+        <v>4.3</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="AG21" t="n">
-        <v>2.72</v>
+        <v>2.56</v>
       </c>
       <c r="AH21" t="n">
         <v>1.4</v>
       </c>
       <c r="AI21" t="n">
-        <v>5.33</v>
+        <v>4.75</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK21" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AL21" t="n">
-        <v>2.11</v>
+        <v>2.18</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.24</v>
+        <v>2.06</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.12</v>
+        <v>1.21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AR21" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AS21" t="n">
-        <v>1.84</v>
+        <v>2.06</v>
       </c>
       <c r="AT21" t="n">
-        <v>2.31</v>
+        <v>2.55</v>
       </c>
       <c r="AU21" t="n">
-        <v>4.75</v>
+        <v>3.65</v>
       </c>
       <c r="AV21" t="n">
-        <v>3.2</v>
+        <v>2.74</v>
       </c>
       <c r="AW21" t="n">
-        <v>2.34</v>
+        <v>2.06</v>
       </c>
       <c r="AX21" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AY21" t="n">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="AZ21" t="n">
-        <v>2.63</v>
+        <v>1.64</v>
       </c>
       <c r="BA21" t="n">
-        <v>1.66</v>
+        <v>2.66</v>
       </c>
       <c r="BB21" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BC21" t="n">
-        <v>1.96</v>
+        <v>1.8</v>
       </c>
       <c r="BD21" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="U22" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL22" t="n">
         <v>1.9</v>
       </c>
-      <c r="Q22" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R22" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U22" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W22" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AM22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ22" t="n">
         <v>1.53</v>
       </c>
-      <c r="Z22" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX22" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY22" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ22" t="n">
-        <v>1.64</v>
-      </c>
       <c r="BA22" t="n">
-        <v>2.66</v>
+        <v>3.46</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>4.24</v>
+        <v>2.65</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="V23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W23" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
         <v>1.36</v>
       </c>
-      <c r="W23" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AK23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL23" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AN23" t="n">
+      <c r="AQ23" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC23" t="n">
         <v>2</v>
       </c>
-      <c r="AO23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2.02</v>
-      </c>
       <c r="BD23" t="n">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.22</v>
+        <v>3.65</v>
       </c>
       <c r="R24" t="n">
-        <v>3.24</v>
+        <v>2.99</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>3.43</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="R25" t="n">
-        <v>2.39</v>
+        <v>2.97</v>
       </c>
       <c r="S25" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="T25" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="U25" t="n">
-        <v>2.78</v>
+        <v>4.33</v>
       </c>
       <c r="V25" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W25" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X25" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM25" t="n">
         <v>1.35</v>
       </c>
-      <c r="W25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X25" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM25" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AN25" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD25" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BE25" t="n">
         <v>1.36</v>
       </c>
-      <c r="AO25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ25" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB25" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC25" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD25" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE25" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BF25" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="R26" t="n">
-        <v>2.99</v>
+        <v>2.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.63</v>
+        <v>3.82</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.09</v>
       </c>
       <c r="U26" t="n">
-        <v>3.43</v>
+        <v>2.78</v>
       </c>
       <c r="V26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM26" t="n">
         <v>1.26</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF26" t="n">
+      <c r="AN26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS26" t="n">
         <v>2.23</v>
       </c>
-      <c r="AG26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AT26" t="n">
-        <v>2.31</v>
+        <v>2.9</v>
       </c>
       <c r="AU26" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="AV26" t="n">
-        <v>3.05</v>
+        <v>2.4</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.84</v>
+        <v>1.56</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AZ26" t="n">
-        <v>1.68</v>
+        <v>2.16</v>
       </c>
       <c r="BA26" t="n">
-        <v>2.58</v>
+        <v>1.89</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.87</v>
+        <v>1.78</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.09</v>
+        <v>3.58</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.57</v>
+        <v>3.85</v>
       </c>
       <c r="R27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W27" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2.59</v>
       </c>
-      <c r="S27" t="n">
-        <v>5</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="U27" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="X27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>6.1</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.08</v>
+        <v>1.39</v>
       </c>
       <c r="AI27" t="n">
-        <v>15.5</v>
+        <v>4.62</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.62</v>
+        <v>1.66</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.46</v>
+        <v>2.09</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.47</v>
+        <v>1.79</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.1</v>
+        <v>2.91</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.89</v>
+        <v>1.96</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="BC27" t="n">
-        <v>3.18</v>
+        <v>1.92</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.36</v>
+        <v>4.25</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.28</v>
+        <v>1.81</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R29" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>2.55</v>
-      </c>
       <c r="S29" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL29" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="W30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="X30" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
         <v>1.22</v>
       </c>
-      <c r="Q30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R30" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U30" t="n">
-        <v>7</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL30" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN30" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AO30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA30" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB30" t="n">
-        <v>0</v>
-      </c>
       <c r="BC30" t="n">
-        <v>1.63</v>
+        <v>2.16</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,133 +6514,133 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.63</v>
+        <v>1.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.7</v>
+        <v>6.36</v>
       </c>
       <c r="R31" t="n">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>4.6</v>
+        <v>1.72</v>
       </c>
       <c r="T31" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
-        <v>2.12</v>
+        <v>9.15</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X31" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="AJ31" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK31" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AN31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB31" t="n">
         <v>1.12</v>
       </c>
-      <c r="AO31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA31" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB31" t="n">
-        <v>0</v>
-      </c>
       <c r="BC31" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.19</v>
+        <v>1.49</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.36</v>
+        <v>3.75</v>
       </c>
       <c r="R33" t="n">
-        <v>12</v>
+        <v>5.7</v>
       </c>
       <c r="S33" t="n">
-        <v>1.72</v>
+        <v>2.1</v>
       </c>
       <c r="T33" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="U33" t="n">
-        <v>9.15</v>
+        <v>6</v>
       </c>
       <c r="V33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W33" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BB33" t="n">
         <v>1.3</v>
       </c>
-      <c r="W33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM33" t="n">
+      <c r="BC33" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BD33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BF33" t="n">
         <v>1.13</v>
-      </c>
-      <c r="AN33" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="AO33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA33" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB33" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="BE33" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>1.28</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>1.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.4</v>
+        <v>5.6</v>
       </c>
       <c r="R34" t="n">
-        <v>2.65</v>
+        <v>10.3</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE34" t="n">
-        <v>2.01</v>
+        <v>1.42</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.76</v>
+        <v>2.55</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI34" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ34" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM34" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AN34" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.49</v>
+        <v>4.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="R35" t="n">
-        <v>5.7</v>
+        <v>1.66</v>
       </c>
       <c r="S35" t="n">
-        <v>2.1</v>
+        <v>4.6</v>
       </c>
       <c r="T35" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="U35" t="n">
-        <v>6</v>
+        <v>2.12</v>
       </c>
       <c r="V35" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="Z35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="AE35" t="n">
-        <v>2.17</v>
+        <v>1.67</v>
       </c>
       <c r="AF35" t="n">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AG35" t="n">
-        <v>3.72</v>
+        <v>2.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AI35" t="n">
-        <v>7.7</v>
+        <v>4.6</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.1</v>
+        <v>1.68</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.67</v>
+        <v>2.02</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AN35" t="n">
-        <v>2.3</v>
+        <v>1.12</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE35" t="n">
         <v>1.75</v>
       </c>
-      <c r="AS35" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BE35" t="n">
-        <v>1.5</v>
-      </c>
       <c r="BF35" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.67</v>
+        <v>2.15</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.51</v>
+        <v>2.9</v>
       </c>
       <c r="R41" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="S41" t="n">
+        <v>3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="U41" t="n">
+        <v>4.24</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="W41" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X41" t="n">
         <v>3.5</v>
       </c>
-      <c r="T41" t="n">
+      <c r="Y41" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL41" t="n">
         <v>1.75</v>
       </c>
-      <c r="U41" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK41" t="n">
+      <c r="AM41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA41" t="n">
         <v>2.45</v>
       </c>
-      <c r="AL41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>2.55</v>
-      </c>
       <c r="BB41" t="n">
-        <v>1.49</v>
+        <v>1.28</v>
       </c>
       <c r="BC41" t="n">
-        <v>3.3</v>
+        <v>2.41</v>
       </c>
       <c r="BD41" t="n">
-        <v>2.36</v>
+        <v>3.14</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="R44" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="S44" t="n">
         <v>2.66</v>
       </c>
       <c r="T44" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="U44" t="n">
-        <v>5</v>
+        <v>4.26</v>
       </c>
       <c r="V44" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="W44" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="X44" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD44" t="n">
         <v>3.34</v>
       </c>
-      <c r="Y44" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.62</v>
-      </c>
       <c r="AE44" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="AG44" t="n">
-        <v>4.3</v>
+        <v>3.14</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="AI44" t="n">
-        <v>9.1</v>
+        <v>5.2</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AK44" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.7</v>
+        <v>2.07</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9156,52 +9156,52 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.14</v>
+        <v>3.82</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>1.87</v>
+        <v>2.67</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.44</v>
+        <v>2.51</v>
       </c>
       <c r="R45" t="n">
-        <v>3.65</v>
+        <v>2.97</v>
       </c>
       <c r="S45" t="n">
-        <v>2.66</v>
+        <v>3.5</v>
       </c>
       <c r="T45" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="U45" t="n">
-        <v>4.26</v>
+        <v>3.8</v>
       </c>
       <c r="V45" t="n">
-        <v>1.38</v>
+        <v>1.79</v>
       </c>
       <c r="W45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR45" t="n">
         <v>2.7</v>
       </c>
-      <c r="X45" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ45" t="n">
+      <c r="AS45" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY45" t="n">
         <v>1.06</v>
       </c>
-      <c r="AK45" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>0</v>
-      </c>
       <c r="AZ45" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB45" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="BC45" t="n">
-        <v>2.07</v>
+        <v>3.3</v>
       </c>
       <c r="BD45" t="n">
-        <v>3.82</v>
+        <v>2.36</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,22 +9469,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T46" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U46" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
         <v>1.49</v>
@@ -9493,16 +9493,16 @@
         <v>2.34</v>
       </c>
       <c r="X46" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Y46" t="n">
         <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB46" t="n">
         <v>1.04</v>
@@ -9532,16 +9532,16 @@
         <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,37 +9550,37 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="BB46" t="n">
         <v>1.28</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>4.13</v>
       </c>
       <c r="T3" t="n">
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>5.96</v>
+        <v>2.7</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X3" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC3" t="n">
         <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AE3" t="n">
         <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB3" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA3" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC3" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>4.71</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>6.8</v>
+        <v>5.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.9</v>
+        <v>3.94</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>13</v>
+        <v>7.9</v>
       </c>
       <c r="AJ5" t="n">
         <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AS5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC5" t="n">
         <v>2.45</v>
       </c>
-      <c r="AT5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>2.91</v>
-      </c>
       <c r="BD5" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3046,40 +3046,40 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AW13" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AX13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AY13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BB13" t="n">
         <v>1.22</v>
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,133 +3165,133 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>1.59</v>
+        <v>2.21</v>
       </c>
       <c r="Q14" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R14" t="n">
-        <v>4.97</v>
+        <v>3.33</v>
       </c>
       <c r="S14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="T14" t="n">
         <v>2.06</v>
       </c>
-      <c r="T14" t="n">
-        <v>2.31</v>
-      </c>
       <c r="U14" t="n">
-        <v>5.48</v>
+        <v>4.6</v>
       </c>
       <c r="V14" t="n">
-        <v>1.31</v>
+        <v>1.47</v>
       </c>
       <c r="W14" t="n">
-        <v>3.1</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC14" t="n">
         <v>2.47</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="BD14" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="BE14" t="n">
         <v>1.47</v>
       </c>
-      <c r="Z14" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA14" t="n">
+      <c r="BF14" t="n">
         <v>1.08</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>2.4</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>3.46</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U15" t="n">
-        <v>2.72</v>
+        <v>3.62</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="X15" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK15" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL15" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AM15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
         <v>1.31</v>
       </c>
-      <c r="AN15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AQ15" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AZ15" t="n">
         <v>2.04</v>
       </c>
       <c r="BA15" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>4.97</v>
       </c>
       <c r="S16" t="n">
-        <v>3.46</v>
+        <v>2.06</v>
       </c>
       <c r="T16" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="U16" t="n">
-        <v>3.62</v>
+        <v>5.48</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W16" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="X16" t="n">
-        <v>3.22</v>
+        <v>2.47</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="Z16" t="n">
-        <v>8.300000000000001</v>
+        <v>5.55</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.49</v>
+        <v>3.8</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AG16" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE16" t="n">
         <v>1.76</v>
       </c>
-      <c r="AM16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF16" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
         <v>3.05</v>
       </c>
       <c r="R17" t="n">
-        <v>3.33</v>
+        <v>3.13</v>
       </c>
       <c r="S17" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS17" t="n">
         <v>2.33</v>
       </c>
-      <c r="T17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U17" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W17" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AT17" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="AU17" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AZ17" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BA17" t="n">
-        <v>2.85</v>
+        <v>2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.16</v>
+        <v>3.36</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="R18" t="n">
-        <v>2.12</v>
+        <v>2.59</v>
       </c>
       <c r="S18" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
-        <v>2.35</v>
+        <v>3.68</v>
       </c>
       <c r="V18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX18" t="n">
         <v>1.3</v>
       </c>
-      <c r="W18" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AY18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="BA18" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.96</v>
+        <v>3.18</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.25</v>
+        <v>2.36</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.22</v>
+        <v>3.35</v>
       </c>
       <c r="R19" t="n">
-        <v>3.24</v>
+        <v>2.65</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AR19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="AT19" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="AU19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AV19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW19" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AX19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BA19" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>3.09</v>
+        <v>1.78</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.57</v>
+        <v>3.62</v>
       </c>
       <c r="R20" t="n">
-        <v>2.59</v>
+        <v>4.24</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>1.58</v>
+        <v>2.13</v>
       </c>
       <c r="U20" t="n">
-        <v>3.68</v>
+        <v>4.5</v>
       </c>
       <c r="V20" t="n">
-        <v>1.85</v>
+        <v>1.36</v>
       </c>
       <c r="W20" t="n">
-        <v>1.85</v>
+        <v>2.85</v>
       </c>
       <c r="X20" t="n">
-        <v>4.6</v>
+        <v>2.81</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="Z20" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>2</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>2.51</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.2</v>
       </c>
-      <c r="AC20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BC20" t="n">
-        <v>3.18</v>
+        <v>2.02</v>
       </c>
       <c r="BD20" t="n">
-        <v>2.36</v>
+        <v>3.84</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R21" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD21" t="n">
         <v>3.78</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W21" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL21" t="n">
         <v>2.19</v>
       </c>
-      <c r="AG21" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ21" t="n">
+      <c r="AM21" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF21" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.78</v>
+        <v>3.58</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>4.24</v>
+        <v>1.87</v>
       </c>
       <c r="S22" t="n">
-        <v>2.31</v>
+        <v>4.45</v>
       </c>
       <c r="T22" t="n">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>4.5</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>2.85</v>
+        <v>3.28</v>
       </c>
       <c r="X22" t="n">
-        <v>2.81</v>
+        <v>2.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.37</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>7.2</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.36</v>
+        <v>3.92</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>2.12</v>
       </c>
       <c r="AG22" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" t="n">
-        <v>6.4</v>
+        <v>4.62</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.8</v>
+        <v>1.66</v>
       </c>
       <c r="AL22" t="n">
-        <v>1.9</v>
+        <v>2.09</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.25</v>
+        <v>1.79</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>1.19</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.51</v>
+        <v>2.14</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AT22" t="n">
-        <v>3.96</v>
+        <v>4.18</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AY22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="BB22" t="n">
         <v>1.16</v>
       </c>
-      <c r="AZ22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="BA22" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="BB22" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BC22" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="BD22" t="n">
-        <v>3.84</v>
+        <v>4.25</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.67</v>
+        <v>1.81</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="S23" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ23" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD23" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sirius</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,79 +5135,79 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.18</v>
+        <v>3.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>2.99</v>
+        <v>2.12</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>3.85</v>
       </c>
       <c r="T24" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="U24" t="n">
-        <v>3.43</v>
+        <v>2.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W24" t="n">
-        <v>3.48</v>
+        <v>3.22</v>
       </c>
       <c r="X24" t="n">
-        <v>2.39</v>
+        <v>2.53</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.51</v>
+        <v>1.46</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
         <v>1.08</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AD24" t="n">
-        <v>4.35</v>
+        <v>3.84</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK24" t="n">
         <v>1.65</v>
       </c>
-      <c r="AF24" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AL24" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.67</v>
+        <v>1.24</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
@@ -5216,7 +5216,7 @@
         <v>1.12</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AR24" t="n">
         <v>1.65</v>
@@ -5231,10 +5231,10 @@
         <v>4.75</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AX24" t="n">
         <v>1.84</v>
@@ -5243,25 +5243,25 @@
         <v>1.5</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.68</v>
+        <v>2.63</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.58</v>
+        <v>1.66</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.65</v>
+        <v>4.25</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Sirius</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,133 +5332,133 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.78</v>
+        <v>2.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.61</v>
+        <v>3.65</v>
       </c>
       <c r="R25" t="n">
-        <v>2.97</v>
+        <v>2.99</v>
       </c>
       <c r="S25" t="n">
-        <v>2.99</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
-        <v>1.75</v>
+        <v>2.36</v>
       </c>
       <c r="U25" t="n">
-        <v>4.33</v>
+        <v>3.43</v>
       </c>
       <c r="V25" t="n">
-        <v>1.61</v>
+        <v>1.26</v>
       </c>
       <c r="W25" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X25" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AL25" t="n">
         <v>2.25</v>
       </c>
-      <c r="X25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AJ25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AL25" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AM25" t="n">
-        <v>1.35</v>
+        <v>1.23</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
       </c>
       <c r="AP25" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AR25" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AS25" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="AT25" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="AU25" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="AV25" t="n">
-        <v>2.05</v>
+        <v>3.05</v>
       </c>
       <c r="AW25" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="AX25" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AY25" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AZ25" t="n">
         <v>1.68</v>
       </c>
       <c r="BA25" t="n">
-        <v>2.35</v>
+        <v>2.58</v>
       </c>
       <c r="BB25" t="n">
-        <v>1.38</v>
+        <v>1.14</v>
       </c>
       <c r="BC25" t="n">
-        <v>2.8</v>
+        <v>1.87</v>
       </c>
       <c r="BD25" t="n">
-        <v>2.77</v>
+        <v>4.65</v>
       </c>
       <c r="BE25" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="BF25" t="n">
-        <v>1.03</v>
+        <v>1.21</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R26" t="n">
-        <v>2.39</v>
+        <v>3.78</v>
       </c>
       <c r="S26" t="n">
-        <v>3.82</v>
+        <v>2.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="U26" t="n">
-        <v>2.78</v>
+        <v>4.49</v>
       </c>
       <c r="V26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X26" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ26" t="n">
         <v>1.35</v>
       </c>
-      <c r="W26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AR26" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AS26" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AT26" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AU26" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AV26" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AW26" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AX26" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AY26" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.89</v>
+        <v>2.66</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.58</v>
+        <v>2.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.85</v>
+        <v>2.61</v>
       </c>
       <c r="R27" t="n">
-        <v>1.87</v>
+        <v>2.97</v>
       </c>
       <c r="S27" t="n">
-        <v>4.45</v>
+        <v>2.99</v>
       </c>
       <c r="T27" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>2.22</v>
+        <v>4.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="W27" t="n">
-        <v>3.28</v>
+        <v>2.25</v>
       </c>
       <c r="X27" t="n">
-        <v>2.44</v>
+        <v>3.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.4</v>
+        <v>11</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>3.92</v>
+        <v>2.27</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.68</v>
+        <v>2.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>2.59</v>
+        <v>5.55</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.39</v>
+        <v>1.08</v>
       </c>
       <c r="AI27" t="n">
-        <v>4.62</v>
+        <v>12.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.12</v>
+        <v>1.03</v>
       </c>
       <c r="AK27" t="n">
-        <v>1.66</v>
+        <v>2.15</v>
       </c>
       <c r="AL27" t="n">
-        <v>2.09</v>
+        <v>1.57</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.91</v>
+        <v>2.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>4.18</v>
+        <v>3.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AW27" t="n">
         <v>1.66</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.96</v>
+        <v>2.35</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.16</v>
+        <v>1.38</v>
       </c>
       <c r="BC27" t="n">
-        <v>1.92</v>
+        <v>2.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>4.25</v>
+        <v>2.77</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.81</v>
+        <v>1.36</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R29" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U29" t="n">
+        <v>6</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W29" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X29" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU29" t="n">
         <v>3.4</v>
       </c>
-      <c r="R29" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU29" t="n">
-        <v>0</v>
-      </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC30" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BD30" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.19</v>
+        <v>4.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.36</v>
+        <v>3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>12</v>
+        <v>1.66</v>
       </c>
       <c r="S31" t="n">
-        <v>1.72</v>
+        <v>4.6</v>
       </c>
       <c r="T31" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="U31" t="n">
-        <v>9.15</v>
+        <v>2.12</v>
       </c>
       <c r="V31" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AI31" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="AJ31" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM31" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK31" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AN31" t="n">
-        <v>3.52</v>
+        <v>1.12</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="BF31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,22 +6711,22 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>10.3</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
@@ -6735,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -6750,40 +6750,40 @@
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6828,13 +6828,13 @@
         <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BD32" t="n">
         <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF32" t="n">
         <v>0</v>
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,133 +6908,133 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.49</v>
+        <v>2.65</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>5.7</v>
+        <v>2.55</v>
       </c>
       <c r="S33" t="n">
-        <v>2.1</v>
+        <v>3.45</v>
       </c>
       <c r="T33" t="n">
-        <v>2.15</v>
+        <v>2.03</v>
       </c>
       <c r="U33" t="n">
-        <v>6</v>
+        <v>2.82</v>
       </c>
       <c r="V33" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="W33" t="n">
-        <v>2.56</v>
+        <v>2.99</v>
       </c>
       <c r="X33" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z33" t="n">
         <v>7</v>
       </c>
       <c r="AA33" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB33" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="AD33" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AE33" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.65</v>
+        <v>1.84</v>
       </c>
       <c r="AG33" t="n">
-        <v>3.72</v>
+        <v>3.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AI33" t="n">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="AJ33" t="n">
         <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>2.1</v>
+        <v>1.67</v>
       </c>
       <c r="AL33" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AN33" t="n">
-        <v>2.3</v>
+        <v>1.41</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS33" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV33" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW33" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX33" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ33" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BD33" t="n">
         <v>3.6</v>
       </c>
-      <c r="BB33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BC33" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="BD33" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BE33" t="n">
-        <v>1.5</v>
+        <v>1.64</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,22 +7105,22 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>1.22</v>
+        <v>2.45</v>
       </c>
       <c r="Q34" t="n">
-        <v>5.6</v>
+        <v>3.4</v>
       </c>
       <c r="R34" t="n">
-        <v>10.3</v>
+        <v>2.65</v>
       </c>
       <c r="S34" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7129,10 +7129,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -7144,40 +7144,40 @@
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.42</v>
+        <v>2.01</v>
       </c>
       <c r="AF34" t="n">
-        <v>2.55</v>
+        <v>1.76</v>
       </c>
       <c r="AG34" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AO34" t="n">
         <v>0</v>
@@ -7222,13 +7222,13 @@
         <v>0</v>
       </c>
       <c r="BC34" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD34" t="n">
         <v>0</v>
       </c>
       <c r="BE34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF34" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>4.63</v>
+        <v>1.19</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.7</v>
+        <v>6.36</v>
       </c>
       <c r="R35" t="n">
-        <v>1.66</v>
+        <v>12</v>
       </c>
       <c r="S35" t="n">
-        <v>4.6</v>
+        <v>1.72</v>
       </c>
       <c r="T35" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="U35" t="n">
-        <v>2.12</v>
+        <v>9.15</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X35" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AD35" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AF35" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.65</v>
+        <v>2.26</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.38</v>
+        <v>1.51</v>
       </c>
       <c r="AI35" t="n">
-        <v>4.6</v>
+        <v>3.86</v>
       </c>
       <c r="AJ35" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AM35" t="n">
         <v>1.13</v>
       </c>
-      <c r="AK35" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AN35" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
         <v>1.12</v>
       </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
       <c r="BC35" t="n">
-        <v>1.85</v>
+        <v>1.74</v>
       </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE35" t="n">
-        <v>1.75</v>
+        <v>2.01</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,22 +8484,22 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R41" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="S41" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T41" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U41" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
         <v>1.49</v>
@@ -8508,16 +8508,16 @@
         <v>2.34</v>
       </c>
       <c r="X41" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Y41" t="n">
         <v>1.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB41" t="n">
         <v>1.04</v>
@@ -8547,16 +8547,16 @@
         <v>1</v>
       </c>
       <c r="AK41" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8565,37 +8565,37 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AU41" t="n">
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="BB41" t="n">
         <v>1.28</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4.26</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK43" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BC43" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="BD43" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="BE43" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BF43" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9189,19 +9189,19 @@
         <v>0</v>
       </c>
       <c r="BB44" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC44" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE44" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,22 +9469,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="R46" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="S46" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>4.24</v>
       </c>
       <c r="V46" t="n">
         <v>1.49</v>
@@ -9493,16 +9493,16 @@
         <v>2.34</v>
       </c>
       <c r="X46" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="Y46" t="n">
         <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AB46" t="n">
         <v>1.04</v>
@@ -9532,16 +9532,16 @@
         <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,37 +9550,37 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.9</v>
+        <v>1.74</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.35</v>
+        <v>2.12</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.23</v>
+        <v>2.48</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="BB46" t="n">
         <v>1.28</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -950,7 +950,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>3.01</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>2.34</v>
+        <v>4.71</v>
       </c>
       <c r="S3" t="n">
-        <v>4.13</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>2.7</v>
+        <v>6.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.44</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>2.48</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>1.36</v>
       </c>
-      <c r="AD3" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.4</v>
+        <v>2.91</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.2</v>
+        <v>2.59</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R4" t="n">
-        <v>4.71</v>
+        <v>3.9</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>6.8</v>
+        <v>5.96</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.9</v>
+        <v>3.94</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AI4" t="n">
-        <v>13</v>
+        <v>7.9</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AS4" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC4" t="n">
         <v>2.45</v>
       </c>
-      <c r="AT4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.91</v>
-      </c>
       <c r="BD4" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>1.95</v>
+        <v>3.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="R5" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>4.13</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>5.96</v>
+        <v>2.7</v>
       </c>
       <c r="V5" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="W5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="X5" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="AC5" t="n">
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AE5" t="n">
         <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AI5" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>2.02</v>
+        <v>1.3</v>
       </c>
       <c r="AO5" t="n">
         <v>0</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
         <v>1.3</v>
       </c>
-      <c r="BA5" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>1.27</v>
-      </c>
       <c r="BC5" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>2.4</v>
+        <v>3.13</v>
       </c>
       <c r="S15" t="n">
-        <v>3.46</v>
+        <v>4.3</v>
       </c>
       <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.83</v>
       </c>
-      <c r="U15" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W15" t="n">
-        <v>2.51</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AL15" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AN15" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z15" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.41</v>
-      </c>
       <c r="AO15" t="n">
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AQ15" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AR15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS15" t="n">
         <v>2.33</v>
       </c>
-      <c r="AS15" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AT15" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AU15" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="AV15" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="AW15" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AX15" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AY15" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="AZ15" t="n">
         <v>2.04</v>
       </c>
       <c r="BA15" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="BB15" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BC15" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="BD15" t="n">
-        <v>2.99</v>
+        <v>3.36</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.46</v>
+        <v>1.52</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>3.13</v>
+        <v>2.4</v>
       </c>
       <c r="S17" t="n">
-        <v>4.3</v>
+        <v>3.46</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U17" t="n">
-        <v>2.72</v>
+        <v>3.62</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="W17" t="n">
-        <v>2.59</v>
+        <v>2.51</v>
       </c>
       <c r="X17" t="n">
-        <v>2.95</v>
+        <v>3.22</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.04</v>
-      </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AL17" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AM17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
         <v>1.31</v>
       </c>
-      <c r="AN17" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AQ17" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AS17" t="n">
-        <v>2.33</v>
+        <v>2.6</v>
       </c>
       <c r="AT17" t="n">
-        <v>3.05</v>
+        <v>3.6</v>
       </c>
       <c r="AU17" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="AV17" t="n">
-        <v>2.32</v>
+        <v>2.17</v>
       </c>
       <c r="AW17" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AX17" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AY17" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AZ17" t="n">
         <v>2.04</v>
       </c>
       <c r="BA17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="BB17" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BC17" t="n">
-        <v>2.33</v>
+        <v>2.5</v>
       </c>
       <c r="BD17" t="n">
-        <v>3.36</v>
+        <v>2.99</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="BF17" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>3.09</v>
+        <v>1.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.57</v>
+        <v>3.7</v>
       </c>
       <c r="R18" t="n">
-        <v>2.59</v>
+        <v>3.78</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.58</v>
+        <v>2.3</v>
       </c>
       <c r="U18" t="n">
-        <v>3.68</v>
+        <v>4.49</v>
       </c>
       <c r="V18" t="n">
-        <v>1.85</v>
+        <v>1.27</v>
       </c>
       <c r="W18" t="n">
-        <v>1.85</v>
+        <v>3.35</v>
       </c>
       <c r="X18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD18" t="n">
         <v>4.6</v>
       </c>
-      <c r="Y18" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>17</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BE18" t="n">
-        <v>1.28</v>
+        <v>1.86</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,130 +4150,130 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="R19" t="n">
-        <v>2.65</v>
+        <v>2.39</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>3.82</v>
       </c>
       <c r="T19" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="U19" t="n">
-        <v>3.45</v>
+        <v>2.78</v>
       </c>
       <c r="V19" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W19" t="n">
-        <v>3.16</v>
+        <v>2.9</v>
       </c>
       <c r="X19" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AD19" t="n">
-        <v>3.5</v>
+        <v>3.78</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW19" t="n">
         <v>1.83</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>1.64</v>
-      </c>
       <c r="AX19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY19" t="n">
         <v>1.35</v>
       </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB19" t="n">
         <v>1.16</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>1.18</v>
-      </c>
       <c r="BC19" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="BD19" t="n">
-        <v>3.94</v>
+        <v>4.25</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="BF19" t="n">
         <v>1.18</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.4</v>
+        <v>2.61</v>
       </c>
       <c r="R21" t="n">
-        <v>2.39</v>
+        <v>2.97</v>
       </c>
       <c r="S21" t="n">
-        <v>3.82</v>
+        <v>2.99</v>
       </c>
       <c r="T21" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="U21" t="n">
-        <v>2.78</v>
+        <v>4.33</v>
       </c>
       <c r="V21" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM21" t="n">
         <v>1.35</v>
       </c>
-      <c r="W21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AN21" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="BD21" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="BE21" t="n">
         <v>1.36</v>
       </c>
-      <c r="AO21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ21" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AR21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS21" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT21" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU21" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AW21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX21" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BC21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="BD21" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="BE21" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BF21" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.58</v>
+        <v>2.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.85</v>
+        <v>3.22</v>
       </c>
       <c r="R22" t="n">
-        <v>1.87</v>
+        <v>3.24</v>
       </c>
       <c r="S22" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.62</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.18</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R23" t="n">
-        <v>3.24</v>
+        <v>1.87</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Israel Israeli Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="R24" t="n">
-        <v>2.12</v>
+        <v>2.65</v>
       </c>
       <c r="S24" t="n">
-        <v>3.85</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="U24" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="V24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W24" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="X24" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="Z24" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.84</v>
+        <v>3.5</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.05</v>
+        <v>1.92</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.72</v>
+        <v>2.83</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.33</v>
+        <v>5.2</v>
       </c>
       <c r="AJ24" t="n">
         <v>1.1</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.11</v>
+        <v>2.14</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.24</v>
+        <v>1.51</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.12</v>
+        <v>1.36</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.26</v>
+        <v>1.68</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.65</v>
+        <v>2.5</v>
       </c>
       <c r="AS24" t="n">
-        <v>1.84</v>
+        <v>2.79</v>
       </c>
       <c r="AT24" t="n">
-        <v>2.31</v>
+        <v>3.94</v>
       </c>
       <c r="AU24" t="n">
-        <v>4.75</v>
+        <v>2.75</v>
       </c>
       <c r="AV24" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="AW24" t="n">
-        <v>2.34</v>
+        <v>1.64</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.84</v>
+        <v>1.35</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.5</v>
+        <v>1.16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>2.63</v>
+        <v>1.92</v>
       </c>
       <c r="BA24" t="n">
-        <v>1.66</v>
+        <v>2.28</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BC24" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="BD24" t="n">
-        <v>4.25</v>
+        <v>3.94</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.9</v>
+        <v>3.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R26" t="n">
-        <v>3.78</v>
+        <v>2.12</v>
       </c>
       <c r="S26" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="T26" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="U26" t="n">
-        <v>4.49</v>
+        <v>2.35</v>
       </c>
       <c r="V26" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W26" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="X26" t="n">
-        <v>2.41</v>
+        <v>2.53</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="Z26" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
       <c r="AA26" t="n">
         <v>1.08</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AD26" t="n">
-        <v>4.3</v>
+        <v>3.84</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.19</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>2.56</v>
+        <v>2.72</v>
       </c>
       <c r="AH26" t="n">
         <v>1.4</v>
       </c>
       <c r="AI26" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AU26" t="n">
         <v>4.75</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AV26" t="n">
-        <v>2.74</v>
+        <v>3.2</v>
       </c>
       <c r="AW26" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="AX26" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA26" t="n">
         <v>1.66</v>
       </c>
-      <c r="AY26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>2.66</v>
-      </c>
       <c r="BB26" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.8</v>
+        <v>1.96</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.86</v>
+        <v>1.79</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.78</v>
+        <v>3.09</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="R27" t="n">
-        <v>2.97</v>
+        <v>2.59</v>
       </c>
       <c r="S27" t="n">
-        <v>2.99</v>
+        <v>5</v>
       </c>
       <c r="T27" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="U27" t="n">
-        <v>4.33</v>
+        <v>3.68</v>
       </c>
       <c r="V27" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="W27" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="X27" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.57</v>
+        <v>1.82</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.27</v>
+        <v>1.93</v>
       </c>
       <c r="AE27" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AG27" t="n">
-        <v>5.55</v>
+        <v>6.1</v>
       </c>
       <c r="AH27" t="n">
         <v>1.08</v>
       </c>
       <c r="AI27" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.15</v>
+        <v>2.62</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.58</v>
+        <v>1.23</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.07</v>
+        <v>2.33</v>
       </c>
       <c r="AS27" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="AT27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="AV27" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AY27" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AZ27" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="BA27" t="n">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="BC27" t="n">
-        <v>2.8</v>
+        <v>3.18</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.49</v>
+        <v>1.19</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.75</v>
+        <v>6.36</v>
       </c>
       <c r="R29" t="n">
-        <v>5.7</v>
+        <v>12</v>
       </c>
       <c r="S29" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="T29" t="n">
-        <v>2.15</v>
+        <v>2.44</v>
       </c>
       <c r="U29" t="n">
-        <v>6</v>
+        <v>9.15</v>
       </c>
       <c r="V29" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="W29" t="n">
-        <v>2.56</v>
+        <v>3.16</v>
       </c>
       <c r="X29" t="n">
-        <v>3.1</v>
+        <v>2.31</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="Z29" t="n">
-        <v>7</v>
+        <v>5.05</v>
       </c>
       <c r="AA29" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB29" t="n">
         <v>1.01</v>
       </c>
-      <c r="AB29" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AC29" t="n">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.9</v>
+        <v>4.45</v>
       </c>
       <c r="AE29" t="n">
-        <v>2.17</v>
+        <v>1.57</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.65</v>
+        <v>2.33</v>
       </c>
       <c r="AG29" t="n">
-        <v>3.72</v>
+        <v>2.26</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="AI29" t="n">
-        <v>7.7</v>
+        <v>3.86</v>
       </c>
       <c r="AJ29" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AK29" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="AL29" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.3</v>
+        <v>3.52</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR29" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS29" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW29" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX29" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA29" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="BC29" t="n">
-        <v>2.29</v>
+        <v>1.74</v>
       </c>
       <c r="BD29" t="n">
-        <v>3.1</v>
+        <v>4.85</v>
       </c>
       <c r="BE29" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,79 +6317,79 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
@@ -6431,19 +6431,19 @@
         <v>0</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,22 +6514,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>4.63</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
         <v>0</v>
@@ -6538,10 +6538,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -6553,40 +6553,40 @@
         <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL31" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6631,13 +6631,13 @@
         <v>0</v>
       </c>
       <c r="BC31" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD31" t="n">
         <v>0</v>
       </c>
       <c r="BE31" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R32" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U32" t="n">
+        <v>6</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W32" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.22</v>
       </c>
-      <c r="Q32" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="S32" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U32" t="n">
-        <v>7</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.63</v>
-      </c>
       <c r="AI32" t="n">
-        <v>3.35</v>
+        <v>7.7</v>
       </c>
       <c r="AJ32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
         <v>1.25</v>
       </c>
-      <c r="AK32" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AO32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP32" t="n">
-        <v>0</v>
-      </c>
       <c r="AQ32" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AS32" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AT32" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AU32" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW32" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX32" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA32" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC32" t="n">
-        <v>1.63</v>
+        <v>2.29</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hermannstadt</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG33" t="n">
         <v>2.65</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="U33" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W33" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="X33" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Y33" t="n">
+      <c r="AH33" t="n">
         <v>1.38</v>
       </c>
-      <c r="Z33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AE33" t="n">
+      <c r="AI33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL33" t="n">
         <v>2.02</v>
       </c>
-      <c r="AF33" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ33" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK33" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL33" t="n">
-        <v>2.01</v>
-      </c>
       <c r="AM33" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.41</v>
+        <v>1.12</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="BD33" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="BF33" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,79 +7302,79 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.36</v>
+        <v>5.6</v>
       </c>
       <c r="R35" t="n">
-        <v>12</v>
+        <v>10.3</v>
       </c>
       <c r="S35" t="n">
-        <v>1.72</v>
+        <v>1.61</v>
       </c>
       <c r="T35" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="U35" t="n">
-        <v>9.15</v>
+        <v>7</v>
       </c>
       <c r="V35" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>2.31</v>
+        <v>1.97</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="Z35" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AD35" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.33</v>
+        <v>2.55</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.26</v>
+        <v>2.06</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.86</v>
+        <v>3.35</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AK35" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7416,19 +7416,19 @@
         <v>0</v>
       </c>
       <c r="BB35" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.74</v>
+        <v>1.63</v>
       </c>
       <c r="BD35" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="BF35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R36" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S36" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T36" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U36" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V36" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="W36" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="X36" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="Z36" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB36" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AD36" t="n">
-        <v>3.38</v>
+        <v>2.09</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.89</v>
+        <v>3.04</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AG36" t="n">
-        <v>3.39</v>
+        <v>6.55</v>
       </c>
       <c r="AH36" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI36" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R37" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S37" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T37" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W37" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X37" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR37" t="n">
         <v>1.85</v>
       </c>
-      <c r="U37" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W37" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="X37" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC37" t="n">
+      <c r="AS37" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD37" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,79 +8484,79 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="Q41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R41" t="n">
         <v>2.95</v>
       </c>
-      <c r="R41" t="n">
-        <v>3.6</v>
-      </c>
       <c r="S41" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="T41" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="U41" t="n">
-        <v>5</v>
+        <v>4.31</v>
       </c>
       <c r="V41" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W41" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="X41" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z41" t="n">
-        <v>10</v>
+        <v>6.95</v>
       </c>
       <c r="AA41" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AD41" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="AE41" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG41" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AH41" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI41" t="n">
-        <v>9.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ41" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK41" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AL41" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AO41" t="n">
         <v>0</v>
@@ -8565,52 +8565,52 @@
         <v>0</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR41" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS41" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT41" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AU41" t="n">
         <v>0</v>
       </c>
       <c r="AV41" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AW41" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AY41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB41" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,79 +8681,79 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.21</v>
+        <v>1.87</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.25</v>
+        <v>3.44</v>
       </c>
       <c r="R42" t="n">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="S42" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="T42" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U42" t="n">
-        <v>4.31</v>
+        <v>4.26</v>
       </c>
       <c r="V42" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="X42" t="n">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z42" t="n">
-        <v>6.95</v>
+        <v>7.2</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AE42" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF42" t="n">
         <v>1.93</v>
       </c>
-      <c r="AF42" t="n">
-        <v>1.81</v>
-      </c>
       <c r="AG42" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AI42" t="n">
-        <v>5.95</v>
+        <v>5.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AK42" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="AL42" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AO42" t="n">
         <v>0</v>
@@ -8798,13 +8798,13 @@
         <v>1.18</v>
       </c>
       <c r="BC42" t="n">
-        <v>2.04</v>
+        <v>2.07</v>
       </c>
       <c r="BD42" t="n">
-        <v>3.92</v>
+        <v>3.82</v>
       </c>
       <c r="BE42" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="BF42" t="n">
         <v>1.14</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Bolivia LFPB</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Real Potosí</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>San Antonio Bulo Bulo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,79 +8878,79 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>4.26</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AI43" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AK43" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AL43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AN43" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AO43" t="n">
         <v>0</v>
@@ -8992,19 +8992,19 @@
         <v>0</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC43" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="BD43" t="n">
-        <v>3.82</v>
+        <v>0</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="BG43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bolivia LFPB</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Real Potosí</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>San Antonio Bulo Bulo</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,79 +9075,79 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4.24</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL44" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9159,13 +9159,13 @@
         <v>0</v>
       </c>
       <c r="AR44" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AS44" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AT44" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
@@ -9174,34 +9174,34 @@
         <v>0</v>
       </c>
       <c r="AW44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AX44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AY44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AZ44" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BA44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="BB44" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC44" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="BD44" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="BE44" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="BF44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="BG44" t="n">
         <v>0</v>
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,22 +9469,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R46" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="S46" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T46" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U46" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
         <v>1.49</v>
@@ -9493,16 +9493,16 @@
         <v>2.34</v>
       </c>
       <c r="X46" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Y46" t="n">
         <v>1.25</v>
       </c>
       <c r="Z46" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB46" t="n">
         <v>1.04</v>
@@ -9532,16 +9532,16 @@
         <v>1</v>
       </c>
       <c r="AK46" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,37 +9550,37 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="BB46" t="n">
         <v>1.28</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.87</v>
+        <v>1.95</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="R3" t="n">
-        <v>4.71</v>
+        <v>3.9</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8</v>
+        <v>5.96</v>
       </c>
       <c r="V3" t="n">
-        <v>1.69</v>
+        <v>1.46</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="X3" t="n">
-        <v>4</v>
+        <v>3.18</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="Z3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.17</v>
+        <v>2.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AG3" t="n">
-        <v>5.9</v>
+        <v>3.94</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.07</v>
+        <v>1.2</v>
       </c>
       <c r="AI3" t="n">
-        <v>13</v>
+        <v>7.9</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.57</v>
+        <v>2.05</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AS3" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BC3" t="n">
         <v>2.45</v>
       </c>
-      <c r="AT3" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.91</v>
-      </c>
       <c r="BD3" t="n">
-        <v>2.59</v>
+        <v>3.25</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R4" t="n">
-        <v>3.9</v>
+        <v>4.71</v>
       </c>
       <c r="S4" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U4" t="n">
-        <v>5.96</v>
+        <v>6.8</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="W4" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AG4" t="n">
-        <v>3.94</v>
+        <v>5.9</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AI4" t="n">
-        <v>7.9</v>
+        <v>13</v>
       </c>
       <c r="AJ4" t="n">
         <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AR4" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AT4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AX4" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AY4" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BB4" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC4" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="BD4" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dhofar</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Dhofar</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3165,37 +3165,37 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>2.21</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>3.33</v>
+        <v>2.4</v>
       </c>
       <c r="S14" t="n">
-        <v>2.33</v>
+        <v>3.46</v>
       </c>
       <c r="T14" t="n">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="U14" t="n">
-        <v>4.6</v>
+        <v>3.62</v>
       </c>
       <c r="V14" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="W14" t="n">
-        <v>2.56</v>
+        <v>2.51</v>
       </c>
       <c r="X14" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>1.02</v>
@@ -3204,91 +3204,91 @@
         <v>1.07</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.62</v>
+        <v>2.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.29</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="AG14" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI14" t="n">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AJ14" t="n">
         <v>1.02</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.08</v>
+        <v>1.95</v>
       </c>
       <c r="AL14" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.28</v>
+        <v>1.39</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.82</v>
+        <v>1.41</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
       </c>
       <c r="AP14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AX14" t="n">
         <v>1.41</v>
       </c>
-      <c r="AQ14" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AY14" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AZ14" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="BA14" t="n">
-        <v>2.85</v>
+        <v>2.2</v>
       </c>
       <c r="BB14" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BC14" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="BD14" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="BF14" t="n">
         <v>1.08</v>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spartak Varna</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3362,133 +3362,133 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="Q15" t="n">
         <v>3.05</v>
       </c>
       <c r="R15" t="n">
-        <v>3.13</v>
+        <v>3.33</v>
       </c>
       <c r="S15" t="n">
-        <v>4.3</v>
+        <v>2.33</v>
       </c>
       <c r="T15" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="U15" t="n">
-        <v>2.72</v>
+        <v>4.6</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="W15" t="n">
-        <v>2.59</v>
+        <v>2.56</v>
       </c>
       <c r="X15" t="n">
-        <v>2.95</v>
+        <v>3.16</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AB15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>1.02</v>
       </c>
-      <c r="AC15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AK15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="BA15" t="n">
         <v>2.85</v>
       </c>
-      <c r="AE15" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP15" t="n">
+      <c r="BB15" t="n">
         <v>1.3</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>2</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>1.25</v>
-      </c>
       <c r="BC15" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="BD15" t="n">
-        <v>3.36</v>
+        <v>3.16</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="BF15" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="BG15" t="n">
         <v>0</v>
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Varna</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,133 +3559,133 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.59</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>4</v>
+        <v>3.05</v>
       </c>
       <c r="R16" t="n">
-        <v>4.97</v>
+        <v>3.13</v>
       </c>
       <c r="S16" t="n">
-        <v>2.06</v>
+        <v>4.3</v>
       </c>
       <c r="T16" t="n">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="U16" t="n">
-        <v>5.48</v>
+        <v>2.72</v>
       </c>
       <c r="V16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>7</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AM16" t="n">
         <v>1.31</v>
       </c>
-      <c r="W16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AF16" t="n">
+      <c r="AN16" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AZ16" t="n">
         <v>2.04</v>
       </c>
-      <c r="AG16" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4</v>
-      </c>
-      <c r="AJ16" t="n">
+      <c r="BA16" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="BF16" t="n">
         <v>1.11</v>
-      </c>
-      <c r="AK16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AL16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>1.19</v>
       </c>
       <c r="BG16" t="n">
         <v>0</v>
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,133 +3756,133 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>2.8</v>
+        <v>1.59</v>
       </c>
       <c r="Q17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4</v>
+        <v>4.97</v>
       </c>
       <c r="S17" t="n">
-        <v>3.46</v>
+        <v>2.06</v>
       </c>
       <c r="T17" t="n">
-        <v>1.83</v>
+        <v>2.31</v>
       </c>
       <c r="U17" t="n">
-        <v>3.62</v>
+        <v>5.48</v>
       </c>
       <c r="V17" t="n">
-        <v>1.44</v>
+        <v>1.31</v>
       </c>
       <c r="W17" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="X17" t="n">
-        <v>3.22</v>
+        <v>2.47</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="Z17" t="n">
-        <v>8.300000000000001</v>
+        <v>5.55</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.42</v>
+        <v>1.23</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.49</v>
+        <v>3.8</v>
       </c>
       <c r="AE17" t="n">
-        <v>2.4</v>
+        <v>1.74</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="AG17" t="n">
-        <v>4.2</v>
+        <v>2.7</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.15</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="AJ17" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.95</v>
+        <v>1.7</v>
       </c>
       <c r="AL17" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="BE17" t="n">
         <v>1.76</v>
       </c>
-      <c r="AM17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.46</v>
-      </c>
       <c r="BF17" t="n">
-        <v>1.08</v>
+        <v>1.19</v>
       </c>
       <c r="BG17" t="n">
         <v>0</v>
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>1.9</v>
+        <v>2.65</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R18" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AD18" t="n">
         <v>3.78</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U18" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X18" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AE18" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AF18" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AL18" t="n">
         <v>2.19</v>
       </c>
-      <c r="AG18" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ18" t="n">
+      <c r="AM18" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BF18" t="n">
         <v>1.18</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP18" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AQ18" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>1.21</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,22 +4102,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.65</v>
+        <v>1.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="R19" t="n">
-        <v>2.39</v>
+        <v>3.78</v>
       </c>
       <c r="S19" t="n">
-        <v>3.82</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="U19" t="n">
-        <v>2.78</v>
+        <v>4.49</v>
       </c>
       <c r="V19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="X19" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AQ19" t="n">
         <v>1.35</v>
       </c>
-      <c r="W19" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AR19" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.23</v>
+        <v>2.06</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AW19" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="AZ19" t="n">
-        <v>2.16</v>
+        <v>1.64</v>
       </c>
       <c r="BA19" t="n">
-        <v>1.89</v>
+        <v>2.66</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.25</v>
+        <v>4.6</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Ironi Kiryat Shmona</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ashdod</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,79 +4347,79 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>1.78</v>
+        <v>2.48</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.62</v>
+        <v>3.35</v>
       </c>
       <c r="R20" t="n">
-        <v>4.24</v>
+        <v>2.65</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>2.88</v>
       </c>
       <c r="T20" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="U20" t="n">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="V20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="X20" t="n">
-        <v>2.81</v>
+        <v>2.62</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.37</v>
+        <v>1.42</v>
       </c>
       <c r="Z20" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.78</v>
+        <v>1.92</v>
       </c>
       <c r="AG20" t="n">
-        <v>3.2</v>
+        <v>2.83</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AL20" t="n">
-        <v>1.9</v>
+        <v>2.14</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>1.51</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
@@ -4428,22 +4428,22 @@
         <v>1.36</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.96</v>
+        <v>3.94</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="AV20" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="AW20" t="n">
         <v>1.64</v>
@@ -4455,25 +4455,25 @@
         <v>1.16</v>
       </c>
       <c r="AZ20" t="n">
-        <v>1.53</v>
+        <v>1.92</v>
       </c>
       <c r="BA20" t="n">
-        <v>3.46</v>
+        <v>2.28</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="BC20" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.84</v>
+        <v>3.94</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Mokawloon</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>IFK Göteborg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,133 +4544,133 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.61</v>
+        <v>3.6</v>
       </c>
       <c r="R21" t="n">
-        <v>2.97</v>
+        <v>2.12</v>
       </c>
       <c r="S21" t="n">
-        <v>2.99</v>
+        <v>3.85</v>
       </c>
       <c r="T21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W21" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.75</v>
       </c>
-      <c r="U21" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="W21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB21" t="n">
+      <c r="AF21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.1</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AK21" t="n">
-        <v>2.15</v>
+        <v>1.65</v>
       </c>
       <c r="AL21" t="n">
-        <v>1.57</v>
+        <v>2.11</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.58</v>
+        <v>1.24</v>
       </c>
       <c r="AO21" t="n">
         <v>0</v>
       </c>
       <c r="AP21" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AQ21" t="n">
-        <v>1.67</v>
+        <v>1.26</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.07</v>
+        <v>1.65</v>
       </c>
       <c r="AS21" t="n">
-        <v>2.7</v>
+        <v>1.84</v>
       </c>
       <c r="AT21" t="n">
-        <v>3.6</v>
+        <v>2.31</v>
       </c>
       <c r="AU21" t="n">
-        <v>2.7</v>
+        <v>4.75</v>
       </c>
       <c r="AV21" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="AW21" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BA21" t="n">
         <v>1.66</v>
       </c>
-      <c r="AX21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AY21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AZ21" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>2.35</v>
-      </c>
       <c r="BB21" t="n">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="BC21" t="n">
-        <v>2.8</v>
+        <v>1.96</v>
       </c>
       <c r="BD21" t="n">
-        <v>2.77</v>
+        <v>4.25</v>
       </c>
       <c r="BE21" t="n">
-        <v>1.36</v>
+        <v>1.79</v>
       </c>
       <c r="BF21" t="n">
-        <v>1.03</v>
+        <v>1.19</v>
       </c>
       <c r="BG21" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Katamon</t>
+          <t>Maccabi Bnei Raina</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ironi Tiberias</t>
+          <t>Maccabi Netanya</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>3.58</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.22</v>
+        <v>3.85</v>
       </c>
       <c r="R22" t="n">
-        <v>3.24</v>
+        <v>1.87</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>4.62</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="R23" t="n">
-        <v>1.87</v>
+        <v>4.24</v>
       </c>
       <c r="S23" t="n">
-        <v>4.45</v>
+        <v>2.31</v>
       </c>
       <c r="T23" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="V23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W23" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X23" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC23" t="n">
         <v>1.28</v>
       </c>
-      <c r="W23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD23" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AI23" t="n">
-        <v>4.62</v>
+        <v>6.4</v>
       </c>
       <c r="AJ23" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AK23" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AL23" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="n">
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.14</v>
+        <v>2.51</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="AT23" t="n">
-        <v>4.18</v>
+        <v>3.96</v>
       </c>
       <c r="AU23" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AV23" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AW23" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="BA23" t="n">
-        <v>1.96</v>
+        <v>3.46</v>
       </c>
       <c r="BB23" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC23" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="BD23" t="n">
-        <v>4.25</v>
+        <v>3.84</v>
       </c>
       <c r="BE23" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BG23" t="n">
         <v>0</v>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.48</v>
+        <v>2.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.35</v>
+        <v>3.22</v>
       </c>
       <c r="R24" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="S24" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AL24" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AS24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AW24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AX24" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AY24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AZ24" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="BA24" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="BB24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BC24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.94</v>
+        <v>0</v>
       </c>
       <c r="BE24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF24" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IFK Göteborg</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,133 +5529,133 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>3.15</v>
+        <v>3.09</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.6</v>
+        <v>2.57</v>
       </c>
       <c r="R26" t="n">
-        <v>2.12</v>
+        <v>2.59</v>
       </c>
       <c r="S26" t="n">
-        <v>3.85</v>
+        <v>5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="U26" t="n">
-        <v>2.35</v>
+        <v>3.68</v>
       </c>
       <c r="V26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="X26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AX26" t="n">
         <v>1.3</v>
       </c>
-      <c r="W26" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="X26" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AY26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ26" t="n">
-        <v>2.63</v>
+        <v>2.06</v>
       </c>
       <c r="BA26" t="n">
-        <v>1.66</v>
+        <v>1.89</v>
       </c>
       <c r="BB26" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="BC26" t="n">
-        <v>1.96</v>
+        <v>3.18</v>
       </c>
       <c r="BD26" t="n">
-        <v>4.25</v>
+        <v>2.36</v>
       </c>
       <c r="BE26" t="n">
-        <v>1.79</v>
+        <v>1.28</v>
       </c>
       <c r="BF26" t="n">
-        <v>1.19</v>
+        <v>1.01</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ghazl El Mehalla</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,133 +5726,133 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>3.09</v>
+        <v>2.78</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="R27" t="n">
-        <v>2.59</v>
+        <v>2.97</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>2.99</v>
       </c>
       <c r="T27" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="U27" t="n">
-        <v>3.68</v>
+        <v>4.33</v>
       </c>
       <c r="V27" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="W27" t="n">
-        <v>1.85</v>
+        <v>2.25</v>
       </c>
       <c r="X27" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z27" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.93</v>
+        <v>2.27</v>
       </c>
       <c r="AE27" t="n">
-        <v>3.28</v>
+        <v>2.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AG27" t="n">
-        <v>6.1</v>
+        <v>5.55</v>
       </c>
       <c r="AH27" t="n">
         <v>1.08</v>
       </c>
       <c r="AI27" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AJ27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AK27" t="n">
-        <v>2.62</v>
+        <v>2.15</v>
       </c>
       <c r="AL27" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.47</v>
+        <v>1.35</v>
       </c>
       <c r="AN27" t="n">
-        <v>1.23</v>
+        <v>1.58</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
       </c>
       <c r="AP27" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="AQ27" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AR27" t="n">
-        <v>2.33</v>
+        <v>2.07</v>
       </c>
       <c r="AS27" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="AT27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AU27" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="AV27" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AW27" t="n">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AX27" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AY27" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AZ27" t="n">
-        <v>2.06</v>
+        <v>1.68</v>
       </c>
       <c r="BA27" t="n">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="BB27" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="BC27" t="n">
-        <v>3.18</v>
+        <v>2.8</v>
       </c>
       <c r="BD27" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="BE27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="BF27" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Metaloglobus</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,79 +6120,79 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.19</v>
+        <v>4.63</v>
       </c>
       <c r="Q29" t="n">
-        <v>6.36</v>
+        <v>3.7</v>
       </c>
       <c r="R29" t="n">
-        <v>12</v>
+        <v>1.66</v>
       </c>
       <c r="S29" t="n">
-        <v>1.72</v>
+        <v>4.6</v>
       </c>
       <c r="T29" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="U29" t="n">
-        <v>9.15</v>
+        <v>2.12</v>
       </c>
       <c r="V29" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.31</v>
+        <v>2.38</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>4.45</v>
+        <v>3.8</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AG29" t="n">
-        <v>2.26</v>
+        <v>2.65</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" t="n">
-        <v>3.86</v>
+        <v>4.6</v>
       </c>
       <c r="AJ29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AM29" t="n">
         <v>1.18</v>
       </c>
-      <c r="AK29" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AN29" t="n">
-        <v>3.52</v>
+        <v>1.12</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
@@ -6234,19 +6234,19 @@
         <v>0</v>
       </c>
       <c r="BB29" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="BC29" t="n">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="BD29" t="n">
-        <v>4.85</v>
+        <v>0</v>
       </c>
       <c r="BE29" t="n">
-        <v>2.01</v>
+        <v>1.75</v>
       </c>
       <c r="BF29" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Miami II</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Crown Legacy</t>
+          <t>Metaloglobus</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>6.36</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>9.15</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>3.86</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,133 +6711,133 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="R32" t="n">
-        <v>5.7</v>
+        <v>10.3</v>
       </c>
       <c r="S32" t="n">
-        <v>2.1</v>
+        <v>1.61</v>
       </c>
       <c r="T32" t="n">
-        <v>2.15</v>
+        <v>2.88</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>3.1</v>
+        <v>1.97</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.31</v>
+        <v>1.66</v>
       </c>
       <c r="Z32" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AD32" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="AE32" t="n">
-        <v>2.17</v>
+        <v>1.42</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.65</v>
+        <v>2.55</v>
       </c>
       <c r="AG32" t="n">
-        <v>3.72</v>
+        <v>2.06</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="AI32" t="n">
-        <v>7.7</v>
+        <v>3.35</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="AK32" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AL32" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.2</v>
+        <v>1.04</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.3</v>
+        <v>3.15</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
       </c>
       <c r="AP32" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AR32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AS32" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AU32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AV32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AW32" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AX32" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AY32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AZ32" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="BA32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="BC32" t="n">
-        <v>2.29</v>
+        <v>1.63</v>
       </c>
       <c r="BD32" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BE32" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="BF32" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>Unirea Slobozia</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,22 +6908,22 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>4.63</v>
+        <v>2.45</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.66</v>
+        <v>2.65</v>
       </c>
       <c r="S33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="V33" t="n">
         <v>0</v>
@@ -6932,10 +6932,10 @@
         <v>0</v>
       </c>
       <c r="X33" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
         <v>0</v>
@@ -6947,40 +6947,40 @@
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.67</v>
+        <v>2.01</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="AG33" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK33" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7025,13 +7025,13 @@
         <v>0</v>
       </c>
       <c r="BC33" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="BD33" t="n">
         <v>0</v>
       </c>
       <c r="BE33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="BF33" t="n">
         <v>0</v>
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Unirea Slobozia</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,133 +7105,133 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.45</v>
+        <v>1.49</v>
       </c>
       <c r="Q34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R34" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="U34" t="n">
+        <v>6</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W34" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X34" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>7</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AU34" t="n">
         <v>3.4</v>
       </c>
-      <c r="R34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU34" t="n">
-        <v>0</v>
-      </c>
       <c r="AV34" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AW34" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AX34" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AY34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BA34" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC34" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="BD34" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BE34" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF34" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>HB</t>
+          <t>Inter Miami II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Crown Legacy</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,22 +7302,22 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>10.3</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="T35" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -7326,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
         <v>0</v>
@@ -7341,40 +7341,40 @@
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AJ35" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AK35" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="AO35" t="n">
         <v>0</v>
@@ -7419,13 +7419,13 @@
         <v>0</v>
       </c>
       <c r="BC35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="BD35" t="n">
         <v>0</v>
       </c>
       <c r="BE35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BF35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Chaco For Ever</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,133 +7499,133 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.98</v>
+        <v>1.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.78</v>
+        <v>3.76</v>
       </c>
       <c r="R36" t="n">
-        <v>4.25</v>
+        <v>3.99</v>
       </c>
       <c r="S36" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="T36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="X36" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AR36" t="n">
         <v>1.85</v>
       </c>
-      <c r="U36" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="W36" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="X36" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Y36" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="Z36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AA36" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC36" t="n">
+      <c r="AS36" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BD36" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BE36" t="n">
         <v>1.71</v>
       </c>
-      <c r="AD36" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP36" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AQ36" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AR36" t="n">
-        <v>2</v>
-      </c>
-      <c r="AS36" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AT36" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU36" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AV36" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AW36" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AX36" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AY36" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AZ36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="BA36" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BB36" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BC36" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="BD36" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BE36" t="n">
-        <v>1.3</v>
-      </c>
       <c r="BF36" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="BG36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Chaco For Ever</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,133 +7696,133 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.76</v>
+        <v>2.78</v>
       </c>
       <c r="R37" t="n">
-        <v>3.99</v>
+        <v>4.25</v>
       </c>
       <c r="S37" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T37" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="U37" t="n">
-        <v>4.33</v>
+        <v>4.8</v>
       </c>
       <c r="V37" t="n">
-        <v>1.38</v>
+        <v>1.68</v>
       </c>
       <c r="W37" t="n">
-        <v>2.97</v>
+        <v>2.05</v>
       </c>
       <c r="X37" t="n">
-        <v>2.62</v>
+        <v>4.3</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.41</v>
+        <v>1.15</v>
       </c>
       <c r="Z37" t="n">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AB37" t="n">
-        <v>1</v>
+        <v>1.16</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.24</v>
+        <v>1.71</v>
       </c>
       <c r="AD37" t="n">
-        <v>3.38</v>
+        <v>2.09</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.89</v>
+        <v>3.04</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AG37" t="n">
-        <v>3.39</v>
+        <v>6.55</v>
       </c>
       <c r="AH37" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>13</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="BD37" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BE37" t="n">
         <v>1.3</v>
       </c>
-      <c r="AI37" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AK37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL37" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AM37" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AN37" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AO37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AQ37" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AR37" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AS37" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AT37" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AU37" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV37" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AW37" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AX37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AY37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AZ37" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BA37" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="BB37" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BC37" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD37" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BE37" t="n">
-        <v>1.71</v>
-      </c>
       <c r="BF37" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="BG37" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>All Boys</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>Deportivo Morón</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,133 +8484,133 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.21</v>
+        <v>2.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.25</v>
+        <v>2.51</v>
       </c>
       <c r="R41" t="n">
-        <v>2.95</v>
+        <v>2.97</v>
       </c>
       <c r="S41" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U41" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>19</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>5.72</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BA41" t="n">
         <v>2.55</v>
       </c>
-      <c r="T41" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U41" t="n">
-        <v>4.31</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="W41" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="X41" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AI41" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="AJ41" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AN41" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AO41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ41" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA41" t="n">
-        <v>0</v>
-      </c>
       <c r="BB41" t="n">
-        <v>1.18</v>
+        <v>1.49</v>
       </c>
       <c r="BC41" t="n">
-        <v>2.04</v>
+        <v>3.3</v>
       </c>
       <c r="BD41" t="n">
-        <v>3.92</v>
+        <v>2.36</v>
       </c>
       <c r="BE41" t="n">
-        <v>1.69</v>
+        <v>1.3</v>
       </c>
       <c r="BF41" t="n">
-        <v>1.14</v>
+        <v>1.05</v>
       </c>
       <c r="BG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Deportes Iquique</t>
+          <t>Inter de Limeira</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,133 +8681,133 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.44</v>
+        <v>2.9</v>
       </c>
       <c r="R42" t="n">
-        <v>3.65</v>
+        <v>3.2</v>
       </c>
       <c r="S42" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>2.02</v>
+        <v>1.85</v>
       </c>
       <c r="U42" t="n">
-        <v>4.26</v>
+        <v>4.24</v>
       </c>
       <c r="V42" t="n">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="W42" t="n">
-        <v>2.7</v>
+        <v>2.34</v>
       </c>
       <c r="X42" t="n">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z42" t="n">
-        <v>7.2</v>
+        <v>9.5</v>
       </c>
       <c r="AA42" t="n">
         <v>1.03</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="AD42" t="n">
-        <v>3.34</v>
+        <v>2.62</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.88</v>
+        <v>2.29</v>
       </c>
       <c r="AF42" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK42" t="n">
         <v>1.93</v>
       </c>
-      <c r="AG42" t="n">
+      <c r="AL42" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="BD42" t="n">
         <v>3.14</v>
       </c>
-      <c r="AH42" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AN42" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AO42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA42" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB42" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="BC42" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="BD42" t="n">
-        <v>3.82</v>
-      </c>
       <c r="BE42" t="n">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="BF42" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BG42" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Confiança</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Inter de Limeira</t>
+          <t>Maranhão</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,22 +9075,22 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="R44" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="S44" t="n">
-        <v>3</v>
+        <v>2.66</v>
       </c>
       <c r="T44" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U44" t="n">
-        <v>4.24</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
         <v>1.49</v>
@@ -9099,16 +9099,16 @@
         <v>2.34</v>
       </c>
       <c r="X44" t="n">
-        <v>3.5</v>
+        <v>3.34</v>
       </c>
       <c r="Y44" t="n">
         <v>1.25</v>
       </c>
       <c r="Z44" t="n">
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AB44" t="n">
         <v>1.04</v>
@@ -9138,16 +9138,16 @@
         <v>1</v>
       </c>
       <c r="AK44" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AL44" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AO44" t="n">
         <v>0</v>
@@ -9156,37 +9156,37 @@
         <v>0</v>
       </c>
       <c r="AQ44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR44" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="AS44" t="n">
-        <v>1.74</v>
+        <v>1.9</v>
       </c>
       <c r="AT44" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="AU44" t="n">
         <v>0</v>
       </c>
       <c r="AV44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW44" t="n">
-        <v>2.48</v>
+        <v>2.23</v>
       </c>
       <c r="AX44" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="AY44" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AZ44" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BA44" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="BB44" t="n">
         <v>1.28</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>All Boys</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Deportivo Morón</t>
+          <t>Deportes Iquique</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,133 +9272,133 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.67</v>
+        <v>1.87</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.51</v>
+        <v>3.44</v>
       </c>
       <c r="R45" t="n">
-        <v>2.97</v>
+        <v>3.65</v>
       </c>
       <c r="S45" t="n">
-        <v>3.5</v>
+        <v>2.66</v>
       </c>
       <c r="T45" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="U45" t="n">
-        <v>3.8</v>
+        <v>4.26</v>
       </c>
       <c r="V45" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
       <c r="X45" t="n">
-        <v>4.6</v>
+        <v>2.78</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="Z45" t="n">
-        <v>17</v>
+        <v>7.2</v>
       </c>
       <c r="AA45" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.02</v>
       </c>
-      <c r="AB45" t="n">
+      <c r="AC45" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB45" t="n">
         <v>1.18</v>
       </c>
-      <c r="AC45" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AO45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP45" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AQ45" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AR45" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS45" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AT45" t="n">
-        <v>5.72</v>
-      </c>
-      <c r="AU45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AV45" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AW45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AX45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AY45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AZ45" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="BA45" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>1.49</v>
-      </c>
       <c r="BC45" t="n">
-        <v>3.3</v>
+        <v>2.07</v>
       </c>
       <c r="BD45" t="n">
-        <v>2.36</v>
+        <v>3.82</v>
       </c>
       <c r="BE45" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="BF45" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Confiança</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Maranhão</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,79 +9469,79 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.95</v>
+        <v>2.21</v>
       </c>
       <c r="Q46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R46" t="n">
         <v>2.95</v>
       </c>
-      <c r="R46" t="n">
-        <v>3.6</v>
-      </c>
       <c r="S46" t="n">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="T46" t="n">
-        <v>1.87</v>
+        <v>2.08</v>
       </c>
       <c r="U46" t="n">
-        <v>5</v>
+        <v>4.31</v>
       </c>
       <c r="V46" t="n">
-        <v>1.49</v>
+        <v>1.35</v>
       </c>
       <c r="W46" t="n">
-        <v>2.34</v>
+        <v>2.82</v>
       </c>
       <c r="X46" t="n">
-        <v>3.34</v>
+        <v>2.7</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="Z46" t="n">
-        <v>10</v>
+        <v>6.95</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AB46" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.38</v>
+        <v>1.23</v>
       </c>
       <c r="AD46" t="n">
-        <v>2.62</v>
+        <v>3.42</v>
       </c>
       <c r="AE46" t="n">
-        <v>2.29</v>
+        <v>1.93</v>
       </c>
       <c r="AF46" t="n">
-        <v>1.54</v>
+        <v>1.81</v>
       </c>
       <c r="AG46" t="n">
-        <v>4.3</v>
+        <v>3.05</v>
       </c>
       <c r="AH46" t="n">
-        <v>1.15</v>
+        <v>1.28</v>
       </c>
       <c r="AI46" t="n">
-        <v>9.1</v>
+        <v>5.95</v>
       </c>
       <c r="AJ46" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="AK46" t="n">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AL46" t="n">
-        <v>1.7</v>
+        <v>2.03</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AN46" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AO46" t="n">
         <v>0</v>
@@ -9550,52 +9550,52 @@
         <v>0</v>
       </c>
       <c r="AQ46" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AR46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AS46" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AT46" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AU46" t="n">
         <v>0</v>
       </c>
       <c r="AV46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AW46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AX46" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AY46" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AZ46" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="BA46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="BB46" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="BC46" t="n">
-        <v>2.41</v>
+        <v>2.04</v>
       </c>
       <c r="BD46" t="n">
-        <v>3.14</v>
+        <v>3.92</v>
       </c>
       <c r="BE46" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="BF46" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="BG46" t="n">
         <v>0</v>

--- a/jogos_2026-05-18.xlsx
+++ b/jogos_2026-05-18.xlsx
@@ -960,12 +960,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>4.71</v>
       </c>
       <c r="S3" t="n">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="U3" t="n">
-        <v>5.96</v>
+        <v>6.8</v>
       </c>
       <c r="V3" t="n">
-        <v>1.46</v>
+        <v>1.69</v>
       </c>
       <c r="W3" t="n">
-        <v>2.44</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
-        <v>3.18</v>
+        <v>4</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="Z3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AA3" t="n">
         <v>1.01</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.36</v>
+        <v>1.64</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.85</v>
+        <v>2.17</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AG3" t="n">
-        <v>3.94</v>
+        <v>5.9</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
       <c r="AI3" t="n">
-        <v>7.9</v>
+        <v>13</v>
       </c>
       <c r="AJ3" t="n">
         <v>1.02</v>
       </c>
       <c r="AK3" t="n">
-        <v>2.05</v>
+        <v>2.57</v>
       </c>
       <c r="AL3" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="AM3" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AN3" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AS3" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="AT3" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="AU3" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="BA3" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.27</v>
+        <v>1.41</v>
       </c>
       <c r="BC3" t="n">
-        <v>2.45</v>
+        <v>2.91</v>
       </c>
       <c r="BD3" t="n">
-        <v>3.25</v>
+        <v>2.59</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kerala Blasters</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Goa</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1195,133 +1195,133 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>1.87</v>
+        <v>3.01</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="R4" t="n">
-        <v>4.71</v>
+        <v>2.34</v>
       </c>
       <c r="S4" t="n">
-        <v>2.62</v>
+        <v>4.13</v>
       </c>
       <c r="T4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
-        <v>6.8</v>
+        <v>2.7</v>
       </c>
       <c r="V4" t="n">
-        <v>1.69</v>
+        <v>1.44</v>
       </c>
       <c r="W4" t="n">
-        <v>2.04</v>
+        <v>2.48</v>
       </c>
       <c r="X4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AA4" t="n">
         <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.15</v>
+        <v>1.06</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.64</v>
+        <v>1.36</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.17</v>
+        <v>2.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.32</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>5.9</v>
+        <v>4</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AI4" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AK4" t="n">
-        <v>2.57</v>
+        <v>1.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AN4" t="n">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BD4" t="n">
         <v>3.2</v>
       </c>
-      <c r="AU4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>2.59</v>
-      </c>
       <c r="BE4" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.03</v>
+        <v>1.13</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kerala Blasters</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goa</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,133 +1392,133 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.01</v>
+        <v>1.95</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.95</v>
+        <v>3.25</v>
       </c>
       <c r="R5" t="n">
-        <v>2.34</v>
+        <v>3.9</v>
       </c>
       <c r="S5" t="n">
-        <v>4.13</v>
+        <v>2.28</v>
       </c>
       <c r="T5" t="n">
         <v>2</v>
       </c>
       <c r="U5" t="n">
-        <v>2.7</v>
+        <v>5.96</v>
       </c>
       <c r="V5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W5" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="X5" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z5" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AA5" t="n">
         <v>1.01</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AC5" t="n">
         <v>1.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="AE5" t="n">
         <v>2.2</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG5" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AI5" t="n">
-        <v>8.5</v>
+        <v>7.9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.77</v>
+        <v>2.05</v>
       </c>
       <c r="AL5" t="n">
-        <v>1.85</v>
+        <v>1.65</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AN5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AZ5" t="n">
         <v>1.3</v>
       </c>
-      <c r="AO5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BC5" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BD5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="BG5" t="n">
         <v>0</v>
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Smail</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Smail</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Ghazl El Mehalla</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,133 +3953,133 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2.65</v>
+        <v>3.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.4</v>
+        <v>2.57</v>
       </c>
       <c r="R18" t="n">
-        <v>2.39</v>
+        <v>2.59</v>
       </c>
       <c r="S18" t="n">
-        <v>3.82</v>
+        <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.09</v>
+        <v>1.58</v>
       </c>
       <c r="U18" t="n">
-        <v>2.78</v>
+        <v>3.68</v>
       </c>
       <c r="V18" t="n">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="W18" t="n">
-        <v>2.9</v>
+        <v>1.85</v>
       </c>
       <c r="X18" t="n">
-        <v>2.59</v>
+        <v>4.6</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="Z18" t="n">
-        <v>6.5</v>
+        <v>17</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.19</v>
+        <v>1.82</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.78</v>
+        <v>1.93</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.76</v>
+        <v>3.28</v>
       </c>
       <c r="AF18" t="n">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.78</v>
+        <v>6.1</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.34</v>
+        <v>1.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>5.16</v>
+        <v>15.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="AK18" t="n">
-        <v>1.56</v>
+        <v>2.62</v>
       </c>
       <c r="AL18" t="n">
-        <v>2.19</v>
+        <v>1.46</v>
       </c>
       <c r="AM18" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.36</v>
+        <v>1.23</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.28</v>
+        <v>1.49</v>
       </c>
       <c r="AQ18" t="n">
-        <v>1.49</v>
+        <v>1.83</v>
       </c>
       <c r="AR18" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AV18" t="n">
         <v>1.85</v>
       </c>
-      <c r="AS18" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AW18" t="n">
-        <v>1.83</v>
+        <v>1.52</v>
       </c>
       <c r="AX18" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AY18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="BA18" t="n">
         <v>1.89</v>
       </c>
       <c r="BB18" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="BC18" t="n">
-        <v>1.95</v>
+        <v>3.18</v>
       </c>
       <c r="BD18" t="n">
-        <v>4.25</v>
+        <v>2.36</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.78</v>
+        <v>1.28</v>
       </c>
       <c r="BF18" t="n">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Arka Gdynia</t>
+          <t>Al Mokawloon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nieciecza</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,133 +4150,133 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>1.9</v>
+        <v>2.78</v>
       </c>
       <c r="Q19" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="R19" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="X19" t="n">
         <v>3.7</v>
       </c>
-      <c r="R19" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="U19" t="n">
-        <v>4.49</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="W19" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="X19" t="n">
-        <v>2.41</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>1.18</v>
       </c>
       <c r="Z19" t="n">
-        <v>5.7</v>
+        <v>11</v>
       </c>
       <c r="AA19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.08</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AI19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AJ19" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC19" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="AH19" t="n">
+      <c r="AK19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
         <v>1.4</v>
       </c>
-      <c r="AI19" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AQ19" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.87</v>
+        <v>2.07</v>
       </c>
       <c r="AS19" t="n">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="AT19" t="n">
-        <v>2.55</v>
+        <v>3.6</v>
       </c>
       <c r="AU19" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="AV19" t="n">
-        <v>2.74</v>
+        <v>2.05</v>
       </c>
       <c r="AW19" t="n">
-        <v>2.06</v>
+        <v>1.66</v>
       </c>
       <c r="AX19" t="n">
-        <v>1.66</v>
+        <v>1.4</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.41</v>
+        <v>1.24</v>
       </c>
       <c r="AZ19" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="BA19" t="n">
-        <v>2.66</v>
+        <v>2.35</v>
       </c>
       <c r="BB19" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="BC19" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="BD19" t="n">
-        <v>4.6</v>
+        <v>2.77</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.86</v>
+        <v>1.36</v>
       </c>
       <c r="BF19" t="n">
-        <v>1.21</v>
+        <v>1.03</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Israel Israeli Premier League</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ironi Kiryat Shmona</t>
+          <t>Arka Gdynia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ashdod</t>
+          <t>Nieciecza</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="Q20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R20" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W20" t="n">
         <v>3.35</v>
       </c>
-      <c r="R20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U20" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="W20" t="n">
-        <v>3.16</v>
-      </c>
       <c r="X20" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="Z20" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AB20" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.22</v>
+        <v>1.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="AG20" t="n">
-        <v>2.83</v>
+        <v>2.56</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AI20" t="n">
-        <v>5.2</v>
+        <v>4.75</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AK20" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="AL20" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.51</v>
+        <v>2.06</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.36</v>
+        <v>1.21</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.68</v>
+        <v>1.35</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.5</v>
+        <v>1.87</v>
       </c>
       <c r="AS20" t="n">
-        <v>2.79</v>
+        <v>2.06</v>
       </c>
       <c r="AT20" t="n">
-        <v>3.94</v>
+        <v>2.55</v>
       </c>
       <c r="AU20" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="AV20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AW20" t="n">
         <v>2.06</v>
       </c>
-      <c r="AW20" t="n">
+      <c r="AX20" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ20" t="n">
         <v>1.64</v>
       </c>
-      <c r="AX20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.92</v>
-      </c>
       <c r="BA20" t="n">
-        <v>2.28</v>
+        <v>2.66</v>
       </c>
       <c r="BB20" t="n">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="BC20" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="BD20" t="n">
-        <v>3.94</v>
+        <v>4.6</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Bnei Raina</t>
+          <t>Hapoel Haifa</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Netanya</t>
+          <t>Bnei Sakhnin</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,133 +4741,133 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>3.58</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="R22" t="n">
-        <v>1.87</v>
+        <v>4.24</v>
       </c>
       <c r="S22" t="n">
-        <v>4.45</v>
+        <v>2.31</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="U22" t="n">
-        <v>2.22</v>
+        <v>4.5</v>
       </c>
       <c r="V22" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W22" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AC22" t="n">
         <v>1.28</v>
       </c>
-      <c r="W22" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AD22" t="n">
-        <v>3.92</v>
+        <v>3.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.68</v>
+        <v>1.98</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.12</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>2.59</v>
+        <v>3.2</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.39</v>
+        <v>1.26</v>
       </c>
       <c r="AI22" t="n">
-        <v>4.62</v>
+        <v>6.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AK22" t="n">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AL22" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.79</v>
+        <v>1.25</v>
       </c>
       <c r="AN22" t="n">
-        <v>1.19</v>
+        <v>2</v>
       </c>
       <c r="AO22" t="n">
         <v>0</v>
       </c>
       <c r="AP22" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.14</v>
+        <v>2.51</v>
       </c>
       <c r="AS22" t="n">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="AT22" t="n">
-        <v>4.18</v>
+        <v>3.96</v>
       </c>
       <c r="AU22" t="n">
-        <v>2.65</v>
+        <v>2.74</v>
       </c>
       <c r="AV22" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AW22" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AX22" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AY22" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AZ22" t="n">
-        <v>2.16</v>
+        <v>1.53</v>
       </c>
       <c r="BA22" t="n">
-        <v>1.96</v>
+        <v>3.46</v>
       </c>
       <c r="BB22" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="BC22" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.25</v>
+        <v>3.84</v>
       </c>
       <c r="BE22" t="n">
-        <v>1.81</v>
+        <v>1.67</v>
       </c>
       <c r="BF22" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="BG22" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Haifa</t>
+          <t>Hapoel Katamon</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Sakhnin</t>
+          <t>Ironi Tiberias</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -4938,133 +4938,133 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>1.78</v>
+        <v>2.2</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="R23" t="n">
-        <v>4.24</v>
+        <v>3.24</v>
       </c>
       <c r="S23" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.98</v>
+        <v>0</v>